--- a/docs/xlsx/jobs-2026-10-08.xlsx
+++ b/docs/xlsx/jobs-2026-10-08.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="730">
   <si>
     <t>Title</t>
   </si>
@@ -61,6 +61,96 @@
     <t>https://www.conservationjobboard.com/job-listing-administration-and-operations-manager-saint-paul-minnesota/6620243982</t>
   </si>
   <si>
+    <t>Aquatic Education Coordinator</t>
+  </si>
+  <si>
+    <t>Kansas Department of Wildlife and Parks</t>
+  </si>
+  <si>
+    <t>Statewide, KS</t>
+  </si>
+  <si>
+    <t>$28 - $29.75 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-aquatic-education-coordinator-statewide-kansas/2101433555</t>
+  </si>
+  <si>
+    <t>Assistant Park/Historic Site Superintendent IV (Assistant Park Superintendent)</t>
+  </si>
+  <si>
+    <t>Texas Parks &amp; Wildlife Department</t>
+  </si>
+  <si>
+    <t>Concan, TX</t>
+  </si>
+  <si>
+    <t>$6,615.99 - $7,615.99 per month</t>
+  </si>
+  <si>
+    <t>general-stewardship-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-assistant-parkhistoric-site-superintendent-iv-assistant-park-superintendent-concan-texas/4333001046</t>
+  </si>
+  <si>
+    <t>Assistant Professor of Biology – Avian Biology</t>
+  </si>
+  <si>
+    <t>Utah State University</t>
+  </si>
+  <si>
+    <t>Logan, UT</t>
+  </si>
+  <si>
+    <t>Faculty / Postdoc</t>
+  </si>
+  <si>
+    <t>$80,000 per year</t>
+  </si>
+  <si>
+    <t>wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-assistant-professor-of-biology--avian-biology-logan-utah/2125723282</t>
+  </si>
+  <si>
+    <t>Associate (Geology/Earth Science)</t>
+  </si>
+  <si>
+    <t>Industrial Economics, Inc.</t>
+  </si>
+  <si>
+    <t>Cambridge, MA</t>
+  </si>
+  <si>
+    <t>$70,000 - $90,000 per year</t>
+  </si>
+  <si>
+    <t>hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-associate-geologyearth-science-cambridge-massachusetts/9536089852</t>
+  </si>
+  <si>
+    <t>Communications Associate</t>
+  </si>
+  <si>
+    <t>Borderlands Restoration Network</t>
+  </si>
+  <si>
+    <t>Patagonia, AZ</t>
+  </si>
+  <si>
+    <t>$26 - $28 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-communications-associate-patagonia-arizona/1359584073</t>
+  </si>
+  <si>
     <t>Community Engagement Director</t>
   </si>
   <si>
@@ -79,6 +169,120 @@
     <t>https://www.conservationjobboard.com/job-listing-community-engagement-director-ventura-california/3718625168</t>
   </si>
   <si>
+    <t>Conservation Project Manager – Mount Desert Island</t>
+  </si>
+  <si>
+    <t>Maine Coast Heritage Trust</t>
+  </si>
+  <si>
+    <t>Mount Desert, ME</t>
+  </si>
+  <si>
+    <t>$70,000 - $80,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-project-manager--mount-desert-island-mount-desert-maine/6288890605</t>
+  </si>
+  <si>
+    <t>Cultural Resources Technician- Temporary</t>
+  </si>
+  <si>
+    <t>SWCA Environmental Consultants</t>
+  </si>
+  <si>
+    <t>Birmingham, AL</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$19.31 - $25.49 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-cultural-resources-technician--temporary-birmingham-alabama/4165063741</t>
+  </si>
+  <si>
+    <t>Charlotte, NC</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-cultural-resources-technician--temporary-charlotte-north-carolina/3239619996</t>
+  </si>
+  <si>
+    <t>Curator of Welfare, Training, and Enrichment</t>
+  </si>
+  <si>
+    <t>Tennessee Aquarium</t>
+  </si>
+  <si>
+    <t>Chattanooga, TN</t>
+  </si>
+  <si>
+    <t>$65,000 - $70,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-curator-of-welfare-training-and-enrichment-chattanooga-tennessee/6789028925</t>
+  </si>
+  <si>
+    <t>Director of Planned Giving</t>
+  </si>
+  <si>
+    <t>Pheasants Forever, Inc., and Quail Forever</t>
+  </si>
+  <si>
+    <t>Negotiable, Remote</t>
+  </si>
+  <si>
+    <t>$85,000 - $125,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-of-planned-giving-negotiable-remote/8185562633</t>
+  </si>
+  <si>
+    <t>ECEF Campaign Volunteer Fellows Program</t>
+  </si>
+  <si>
+    <t>Eugene Clean Energy Fund</t>
+  </si>
+  <si>
+    <t>Eugene, OR</t>
+  </si>
+  <si>
+    <t>Unpaid</t>
+  </si>
+  <si>
+    <t>This is an unpaid role.</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-ecef-campaign-volunteer-fellows-program-eugene-oregon/5335757489</t>
+  </si>
+  <si>
+    <t>Elephant Specialist</t>
+  </si>
+  <si>
+    <t>White Oak Conservation</t>
+  </si>
+  <si>
+    <t>Yulee, FL</t>
+  </si>
+  <si>
+    <t>Negotiable</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-elephant-specialist-yulee-florida/7440554556</t>
+  </si>
+  <si>
     <t>Executive Director</t>
   </si>
   <si>
@@ -97,12 +301,24 @@
     <t>https://www.conservationjobboard.com/job-listing-executive-director-la-veta-colorado/6729198041</t>
   </si>
   <si>
+    <t>National Speleological Society</t>
+  </si>
+  <si>
+    <t>Huntsville, AL</t>
+  </si>
+  <si>
+    <t>$130,000 - $150,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-executive-director-huntsville-alabama/8466727153</t>
+  </si>
+  <si>
     <t>Farm Bill Wildlife Biologist I, II, or III</t>
   </si>
   <si>
-    <t>Pheasants Forever, Inc., and Quail Forever</t>
-  </si>
-  <si>
     <t>Selby, Mound City, or Leola &amp; Wall, SD</t>
   </si>
   <si>
@@ -113,6 +329,1881 @@
   </si>
   <si>
     <t>https://www.conservationjobboard.com/job-listing-farm-bill-wildlife-biologist-i-ii-or-iii-selby-mound-city-or-leola--wall-south-dakota/9268428187</t>
+  </si>
+  <si>
+    <t>First Year Naturalist Educator</t>
+  </si>
+  <si>
+    <t>Canyonlands Field Institute</t>
+  </si>
+  <si>
+    <t>Moab, UT</t>
+  </si>
+  <si>
+    <t>$175 per day</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-first-year-naturalist-educator-moab-utah/5847646555</t>
+  </si>
+  <si>
+    <t>Fishery Observer Support Liaison</t>
+  </si>
+  <si>
+    <t>A.I.S. Inc.</t>
+  </si>
+  <si>
+    <t>N. Dartmouth, MA</t>
+  </si>
+  <si>
+    <t>$25 - $27.50 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fishery-observer-support-liaison-n-dartmouth-massachusetts/6037699671</t>
+  </si>
+  <si>
+    <t>Hand Crew Squad Boss, Wildland Fire Management Lead</t>
+  </si>
+  <si>
+    <t>Washington State Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>Battle Ground or Chehalis, WA</t>
+  </si>
+  <si>
+    <t>$45,924 - $61,332 per year</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-hand-crew-squad-boss-wildland-fire-management-lead-battle-ground-or-chehalis-washington/1095224319</t>
+  </si>
+  <si>
+    <t>Hunter Education Coordinator</t>
+  </si>
+  <si>
+    <t>Pratt, KS</t>
+  </si>
+  <si>
+    <t>$35 - $37 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-hunter-education-coordinator-pratt-kansas/8111849138</t>
+  </si>
+  <si>
+    <t>Intergovernmental Affairs Specialist</t>
+  </si>
+  <si>
+    <t>Buena Vista Rancheria of Me-Wuk Indians</t>
+  </si>
+  <si>
+    <t>Ione, CA</t>
+  </si>
+  <si>
+    <t>$30 - $35 per hour</t>
+  </si>
+  <si>
+    <t>policy-and-law-admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-intergovernmental-affairs-specialist-ione-california/8723778798</t>
+  </si>
+  <si>
+    <t>Natural Resource Officer I/Game Warden Testing and Assessment Opportunity</t>
+  </si>
+  <si>
+    <t>$25.94 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-natural-resource-officer-igame-warden-testing-and-assessment-opportunity-statewide-kansas/3754479193</t>
+  </si>
+  <si>
+    <t>Natural Resources Safety &amp; Training Coordinator (Bilingual)</t>
+  </si>
+  <si>
+    <t>Conservation Corps North Bay</t>
+  </si>
+  <si>
+    <t>San Rafael, CA</t>
+  </si>
+  <si>
+    <t>$70,304 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-natural-resources-safety--training-coordinator-bilingual-san-rafael-california/6723906402</t>
+  </si>
+  <si>
+    <t>Project Forester</t>
+  </si>
+  <si>
+    <t>South Carolina Forestry Commission</t>
+  </si>
+  <si>
+    <t>Williamsburg County, SC</t>
+  </si>
+  <si>
+    <t>$50,598 - $58,470 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-project-forester-williamsburg-county-south-carolina/9419504158</t>
+  </si>
+  <si>
+    <t>Regional Park Superintendent II</t>
+  </si>
+  <si>
+    <t>County of Los Angeles, Department of Parks and Recreation</t>
+  </si>
+  <si>
+    <t>Puenta Hills, CA</t>
+  </si>
+  <si>
+    <t>$89,930 - $121,188 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-regional-park-superintendent-ii-puenta-hills-california/8942013968</t>
+  </si>
+  <si>
+    <t>Regional Park Superintendent III</t>
+  </si>
+  <si>
+    <t>$104,006 - $140,161 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-regional-park-superintendent-iii-puenta-hills-california/1797813630</t>
+  </si>
+  <si>
+    <t>Sanctuary Wildlife Keeper</t>
+  </si>
+  <si>
+    <t>KSTR Wildlife Rescue</t>
+  </si>
+  <si>
+    <t>Quepos, Latin America</t>
+  </si>
+  <si>
+    <t>$0 - $400 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-sanctuary-wildlife-keeper-quepos-latin-america/8736441497</t>
+  </si>
+  <si>
+    <t>Sawyer/Wood Products Development</t>
+  </si>
+  <si>
+    <t>Springboard Forestry LLC</t>
+  </si>
+  <si>
+    <t>Timber, OR</t>
+  </si>
+  <si>
+    <t>$23 - $28 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-sawyer--wood-products-development-timber-oregon/5090473750</t>
+  </si>
+  <si>
+    <t>Science and Policy Analyst</t>
+  </si>
+  <si>
+    <t>Friends of the Everglades</t>
+  </si>
+  <si>
+    <t>Stuart, FL</t>
+  </si>
+  <si>
+    <t>$60,000 - $70,000 per year</t>
+  </si>
+  <si>
+    <t>ecology-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-science-and-policy-analyst-stuart-florida/9254511351</t>
+  </si>
+  <si>
+    <t>Senior Commercial Manager, Canada</t>
+  </si>
+  <si>
+    <t>Marine Stewardship Council</t>
+  </si>
+  <si>
+    <t>Toronto (Hybrid); or remote based in Vancouver, Halifax or Montreal, Canada</t>
+  </si>
+  <si>
+    <t>Competitive</t>
+  </si>
+  <si>
+    <t>admin-leadership-sustainability-fisheries</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-commercial-manager-canada-toronto-ontario-canada/8517754469</t>
+  </si>
+  <si>
+    <t>Senior Natural Resources Specialist</t>
+  </si>
+  <si>
+    <t>CEHMM</t>
+  </si>
+  <si>
+    <t>Carlsbad, NM</t>
+  </si>
+  <si>
+    <t>$30 - $38 per hour</t>
+  </si>
+  <si>
+    <t>ecology-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-natural-resources-specialist-carlsbad-new-mexico/7100945755</t>
+  </si>
+  <si>
+    <t>Senior Statewide Conservation Project Manager</t>
+  </si>
+  <si>
+    <t>Colorado Open Lands</t>
+  </si>
+  <si>
+    <t>Lakewood, CO</t>
+  </si>
+  <si>
+    <t>$82,000 - $100,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-statewide-conservation-project-manager-lakewood-colorado/2198602890</t>
+  </si>
+  <si>
+    <t>Shooting Sports and Range Coordinator</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-shooting-sports-and-range-coordinator-pratt-kansas/3634097065</t>
+  </si>
+  <si>
+    <t>Southeastern States Conservation Manager</t>
+  </si>
+  <si>
+    <t>The Wilderness Society</t>
+  </si>
+  <si>
+    <t>Remote, Remote</t>
+  </si>
+  <si>
+    <t>$75,000 - $85,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-southeastern-states-conservation-manager-remote-remote/3182746905</t>
+  </si>
+  <si>
+    <t>Statewide Conservation Project Manager</t>
+  </si>
+  <si>
+    <t>$70,000 - $82,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-statewide-conservation-project-manager-lakewood-colorado/7882087123</t>
+  </si>
+  <si>
+    <t>Turkey Project Temporary Worker (2 Positions Available)</t>
+  </si>
+  <si>
+    <t>Iowa Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>Various, IA</t>
+  </si>
+  <si>
+    <t>$15.25 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-turkey-project-temporary-worker-2-positions-available-various-iowa/8786559685</t>
+  </si>
+  <si>
+    <t>Waterfowl Banding Technician</t>
+  </si>
+  <si>
+    <t>University of Arkansas at Monticello</t>
+  </si>
+  <si>
+    <t>Monticello, AR</t>
+  </si>
+  <si>
+    <t>$16 - $17 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-waterfowl-banding-technician-monticello-arkansas/7002996842</t>
+  </si>
+  <si>
+    <t>Watershed Implementation Lead (Environmental Specialist 4) (Two Positions)</t>
+  </si>
+  <si>
+    <t>WA State Department of Ecology</t>
+  </si>
+  <si>
+    <t>Spokane, WA</t>
+  </si>
+  <si>
+    <t>$69,348 - $93,288 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-watershed-implementation-lead-environmental-specialist-4-two-positions-spokane-washington/6946785102</t>
+  </si>
+  <si>
+    <t>Yellowstone Winter Ecology Field Instructor - Winter 2027</t>
+  </si>
+  <si>
+    <t>Ecology Project International</t>
+  </si>
+  <si>
+    <t>Missoula, MT</t>
+  </si>
+  <si>
+    <t>$173 - $191 per day</t>
+  </si>
+  <si>
+    <t>ecology-environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-yellowstone-winter-ecology-field-instructor---winter-2027-missoula-montana/9882273116</t>
+  </si>
+  <si>
+    <t>Director of Land Conservation</t>
+  </si>
+  <si>
+    <t>Cibolo Center for Conservation</t>
+  </si>
+  <si>
+    <t>Boerne, Texas, United States</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t>80,000 - 100,000</t>
+  </si>
+  <si>
+    <t>Conservation</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/director-of-land-conservation/</t>
+  </si>
+  <si>
+    <t>Energy Assessor 1</t>
+  </si>
+  <si>
+    <t>Elysian Energy</t>
+  </si>
+  <si>
+    <t>Laurel, Maryland, United States</t>
+  </si>
+  <si>
+    <t>40,000 - 60,000</t>
+  </si>
+  <si>
+    <t>Energy Efficiency</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/energy-assessor-1/</t>
+  </si>
+  <si>
+    <t>Advocate (bilingual in English and Spanish)</t>
+  </si>
+  <si>
+    <t>The Network/La Red</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 59160.00 - 59160.00/year</t>
+  </si>
+  <si>
+    <t>Lgbtq, Victim Support</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2b12970c8fc14cb1acc5890ffece59bc-advocate-bilingual-in-english-and-spanish-the-networkla-red-boston</t>
+  </si>
+  <si>
+    <t>Analista de Alianzas y Estrategias para Fundraising</t>
+  </si>
+  <si>
+    <t>Por el Mar</t>
+  </si>
+  <si>
+    <t>San Isidro, Provincia de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>USD 1700.00/month</t>
+  </si>
+  <si>
+    <t>Animals, Environment, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8473b80cd59b4e01b681fe45cec6bffa-analista-de-alianzas-y-estrategias-para-fundraising-por-el-mar-san-isidro</t>
+  </si>
+  <si>
+    <t>Assistant Director, Native American Affairs</t>
+  </si>
+  <si>
+    <t>United States Conference of Catholic Bishops</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 93000.00/year</t>
+  </si>
+  <si>
+    <t>Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/abe4d093630e4c48bc494a4ae0fbb0c1-assistant-director-native-american-affairs-united-states-conference-of-catholic-bishops-washington</t>
+  </si>
+  <si>
+    <t>Assistant Program Director, Camp Naru</t>
+  </si>
+  <si>
+    <t>YS Kim Foundation</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Children Youth, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4f707a1fea57403b94c44726984de059-assistant-program-director-camp-naru-ys-kim-foundation-new-york</t>
+  </si>
+  <si>
+    <t>Assistente de Recrutamento e Acolhimento</t>
+  </si>
+  <si>
+    <t>Eco Caminhos</t>
+  </si>
+  <si>
+    <t>Nova Friburgo, Rio de Janeiro, BR</t>
+  </si>
+  <si>
+    <t>BRL 1621.00/month</t>
+  </si>
+  <si>
+    <t>Agriculture, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cb187ade5b88499291930eda7d5205d2-assistente-de-recrutamento-e-acolhimento-eco-caminhos-nova-friburgo</t>
+  </si>
+  <si>
+    <t>Associate Art Director</t>
+  </si>
+  <si>
+    <t>Everytown For Gun Safety</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/255ca238b52e461f88886a48516884d1-associate-art-director-everytown-for-gun-safety-new-york</t>
+  </si>
+  <si>
+    <t>Associate Attorney</t>
+  </si>
+  <si>
+    <t>Egality Law LLP</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/d7ff01b04b5f4596a5ad39148f391c29-associate-attorney-egality-law-llp-los-angeles</t>
+  </si>
+  <si>
+    <t>Associate Director of Development</t>
+  </si>
+  <si>
+    <t>Katonah Museum of Art</t>
+  </si>
+  <si>
+    <t>Katonah, New York</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5ebbf3e4867a41e1817d390003ca5ae8-associate-director-of-development-katonah-museum-of-art-katonah</t>
+  </si>
+  <si>
+    <t>Associate Director of State Policy and Advocacy</t>
+  </si>
+  <si>
+    <t>American Kidney Fund</t>
+  </si>
+  <si>
+    <t>Rockville, Maryland</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2794d563802e4932885d57fc0dd9f0eb-associate-director-of-state-policy-and-advocacy-american-kidney-fund-rockville</t>
+  </si>
+  <si>
+    <t>Attorney, Adolescent Representation Unit</t>
+  </si>
+  <si>
+    <t>Brooklyn Defender Services</t>
+  </si>
+  <si>
+    <t>Queens, NY</t>
+  </si>
+  <si>
+    <t>USD 101000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/00ba652ddfa749c4b3e5d14a8c85b237-attorney-adolescent-representation-unit-brooklyn-defender-services-queens</t>
+  </si>
+  <si>
+    <t>Bilingual Client Services Coordinator</t>
+  </si>
+  <si>
+    <t>COMMUNITY SERVINGS INC</t>
+  </si>
+  <si>
+    <t>JAMAICA, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 20.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Health Medicine, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7035a80efb4440ccabfeedf52e488df3-bilingual-client-services-coordinator-community-servings-inc-jamaica</t>
+  </si>
+  <si>
+    <t>Building Green Futures Lead Trainer</t>
+  </si>
+  <si>
+    <t>Building Futures (Rhode Island)</t>
+  </si>
+  <si>
+    <t>Providence, Rhode Island</t>
+  </si>
+  <si>
+    <t>USD 72800.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a57d66b034984e22977676f653d411c8-building-green-futures-lead-trainer-building-futures-rhode-island-providence</t>
+  </si>
+  <si>
+    <t>Business Development Officer</t>
+  </si>
+  <si>
+    <t>Equimundo</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8643de3ce380451aa736f449a4441cb0-business-development-officer-equimundo-washington</t>
+  </si>
+  <si>
+    <t>Chapter Organizer</t>
+  </si>
+  <si>
+    <t>Kentuckians For The Commonwealth</t>
+  </si>
+  <si>
+    <t>London, Kentucky</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Civic Engagement, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/70b4804a845b4a7797b12427d841c761-chapter-organizer-kentuckians-for-the-commonwealth-london</t>
+  </si>
+  <si>
+    <t>Chief Operating Officer</t>
+  </si>
+  <si>
+    <t>EveryMind</t>
+  </si>
+  <si>
+    <t>USD 210000.00 - 220000.00/year</t>
+  </si>
+  <si>
+    <t>Mental Health, Children Youth, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/4fae2ef1e32b413088f28f1aa631d58f-chief-operating-officer-everymind-rockville</t>
+  </si>
+  <si>
+    <t>Chief Revenue Officer</t>
+  </si>
+  <si>
+    <t>Re:wild</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 200000.00 - 250000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Environment, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/80e833c7b9314f8681d8c4de9b9d4647-chief-revenue-officer-rewild-austin</t>
+  </si>
+  <si>
+    <t>Citywide Director – Employment Law Unit</t>
+  </si>
+  <si>
+    <t>The Legal Aid Society - New York City</t>
+  </si>
+  <si>
+    <t>USD 166000.00 - 175200.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a7b620773b654d1d9955e4b8940dd349-citywide-director-employment-law-unit-the-legal-aid-society-new-york-city-new-york</t>
+  </si>
+  <si>
+    <t>Civic Engagement Organizer - Iowa</t>
+  </si>
+  <si>
+    <t>United Today, Stronger Tomorrow</t>
+  </si>
+  <si>
+    <t>Remote (Iowa)</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/980f75b8af7045f99479bef8da96fccd-civic-engagement-organizer-iowa-united-today-stronger-tomorrow-salt-lake-city</t>
+  </si>
+  <si>
+    <t>Community Engagement Associate - Spanish</t>
+  </si>
+  <si>
+    <t>NYC Kids RISE</t>
+  </si>
+  <si>
+    <t>Long Island City, New York</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4f42c0f2f158411396ea93d398abb9a0-community-engagement-associate-spanish-nyc-kids-rise-long-island-city</t>
+  </si>
+  <si>
+    <t>Community Reentry Program Lead</t>
+  </si>
+  <si>
+    <t>The Phoenix</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 73000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Substance Abuse Addiction, Mental Health, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1445f459900740018e1f56cdc786f26d-community-reentry-program-lead-the-phoenix-boston</t>
+  </si>
+  <si>
+    <t>Consultoría en psiquiatría</t>
+  </si>
+  <si>
+    <t>Compañeros En Salud</t>
+  </si>
+  <si>
+    <t>Remote (MX)</t>
+  </si>
+  <si>
+    <t>MXN 25000.00 - 25000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Human Rights Civil Liberties, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a7f8a590112f4ff1b5b4fb047dc5efa2-consultoria-en-psiquiatria-companeros-en-salud-angel-albino-corzo</t>
+  </si>
+  <si>
+    <t>Development Coordinator</t>
+  </si>
+  <si>
+    <t>Two Ten Footwear Foundation</t>
+  </si>
+  <si>
+    <t>Remote (Massachusetts)</t>
+  </si>
+  <si>
+    <t>USD 47661.24 - 50237.19/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Education, Disaster Relief</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e977a4ef2c924064b2be2e81510b4d03-development-coordinator-two-ten-footwear-foundation-waltham</t>
+  </si>
+  <si>
+    <t>Development Manager</t>
+  </si>
+  <si>
+    <t>Pro Bono Institute</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/655c0c2ca2744a739098b68684916b30-development-manager-pro-bono-institute-washington</t>
+  </si>
+  <si>
+    <t>Development Manager at Jane Doe Inc.</t>
+  </si>
+  <si>
+    <t>Jane Doe Inc</t>
+  </si>
+  <si>
+    <t>USD 83000.00 - 87000.00/year</t>
+  </si>
+  <si>
+    <t>Victim Support, Sexual Abuse Human Trafficking</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/e444cf8e49f0411cbcf794e7cb7c4079-development-manager-at-jane-doe-inc-jane-doe-inc-boston</t>
+  </si>
+  <si>
+    <t>Development Specialist - Remote</t>
+  </si>
+  <si>
+    <t>PARKINSON &amp; MOVEMENT DISORDER ALLIANCE</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 57000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2989b5cb8b894efb82f53861a67707c5-development-specialist-remote-parkinson-movement-disorder-alliance-phoenix</t>
+  </si>
+  <si>
+    <t>Digital Content Manager at Lincoln Center Theater</t>
+  </si>
+  <si>
+    <t>Lincoln Center Theater - New York</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/228e62088a3445ce9f419cfdcb656da3-digital-content-manager-at-lincoln-center-theater-lincoln-center-theater-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Director of Administration and Finance</t>
+  </si>
+  <si>
+    <t>Weeksville Heritage Center</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1647407592204ba8887d20aadc2865d4-director-of-administration-and-finance-weeksville-heritage-center-kings-county</t>
+  </si>
+  <si>
+    <t>Director of Board &amp; Presidential Relations</t>
+  </si>
+  <si>
+    <t>University of Vermont Foundation</t>
+  </si>
+  <si>
+    <t>Burlington, Vermont</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/006b7d4f2e3745e79b903d55356c7abf-director-of-board-presidential-relations-university-of-vermont-foundation-burlington</t>
+  </si>
+  <si>
+    <t>Director of Grant Programs</t>
+  </si>
+  <si>
+    <t>Disaster Relief, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7caabbfff909434889e6f2b780e36571-director-of-grant-programs-two-ten-footwear-foundation-waltham</t>
+  </si>
+  <si>
+    <t>Director of Internal Operations at NECHAMA - Jewish Response to Disaster</t>
+  </si>
+  <si>
+    <t>NECHAMA - Jewish Response to Disaster</t>
+  </si>
+  <si>
+    <t>Disaster Relief, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d0ebc90255f744359a366ebde90d48ec-director-of-internal-operations-at-nechama-jewish-response-to-disaster-nechama-jewish-response-to-disaster-saint-paul</t>
+  </si>
+  <si>
+    <t>Donor Engagement Specialist, Travel</t>
+  </si>
+  <si>
+    <t>Earthjustice</t>
+  </si>
+  <si>
+    <t>USD 91400.00 - 119400.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/fdb15ae37cb6447db514c129038bf340-donor-engagement-specialist-travel-earthjustice-san-francisco</t>
+  </si>
+  <si>
+    <t>Editorial/Administrative Assistant</t>
+  </si>
+  <si>
+    <t>American Association for Justice</t>
+  </si>
+  <si>
+    <t>USD 49000.00 - 52000.00/year</t>
+  </si>
+  <si>
+    <t>Crime Safety, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/30b7f3bf1828478d892052befaefec62-editorialadministrative-assistant-american-association-for-justice-washington</t>
+  </si>
+  <si>
+    <t>ELL Instructor at Rikers Island (Full-Time or Part-Time)</t>
+  </si>
+  <si>
+    <t>The Petey Greene Program</t>
+  </si>
+  <si>
+    <t>USD 67000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Prison Reform</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/75120d564e604797825e3f2872fd7ce8-ell-instructor-at-rikers-island-full-time-or-part-time-the-petey-greene-program-new-york</t>
+  </si>
+  <si>
+    <t>Event Coordinator</t>
+  </si>
+  <si>
+    <t>Buckley Hall Events</t>
+  </si>
+  <si>
+    <t>USD 40000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/19e4d5237bc449888b39221a709e3693-event-coordinator-buckley-hall-events-katonah</t>
+  </si>
+  <si>
+    <t>Executive Assistant</t>
+  </si>
+  <si>
+    <t>The C.A.R.D.Board Project</t>
+  </si>
+  <si>
+    <t>Remote (Dallas, Texas)</t>
+  </si>
+  <si>
+    <t>USD 21.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Science Technology, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3213b7b9c92247e5a17c805183c21400-executive-assistant-the-cardboard-project-dallas</t>
+  </si>
+  <si>
+    <t>Kellogg-Hubbard Library</t>
+  </si>
+  <si>
+    <t>Montpelier, Vermont</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Communications Access</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/84ea6d7313e9414cb412915c467db9ff-executive-director-kellogg-hubbard-library-montpelier</t>
+  </si>
+  <si>
+    <t>Multnomah Athletic Foundation</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/e34d65209bf54e8e9c0cdc87f3372286-executive-director-multnomah-athletic-foundation-portland</t>
+  </si>
+  <si>
+    <t>Facilitador/a Educativo/a en Michoacán ( Morelia o Capula )</t>
+  </si>
+  <si>
+    <t>Educación para Compartir - México</t>
+  </si>
+  <si>
+    <t>Morelia, Michoacán, MX</t>
+  </si>
+  <si>
+    <t>MXN 15750.00 - 15750.00/month</t>
+  </si>
+  <si>
+    <t>Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/21ccf6de0f9a43efbe2ef0dcd5fccca0-facilitadora-educativoa-en-michoacan-morelia-o-capula-educacion-para-compartir-mexico-morelia</t>
+  </si>
+  <si>
+    <t>Facilities Director</t>
+  </si>
+  <si>
+    <t>David Brower Center</t>
+  </si>
+  <si>
+    <t>Berkeley, CA</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e8c7587b691f44c8a6933168e829e158-facilities-director-david-brower-center-berkeley</t>
+  </si>
+  <si>
+    <t>Finance &amp; Administration Officer</t>
+  </si>
+  <si>
+    <t>Coordinating Committee for International Voluntary Service</t>
+  </si>
+  <si>
+    <t>Remote (HU)</t>
+  </si>
+  <si>
+    <t>EUR 1500.00/month</t>
+  </si>
+  <si>
+    <t>Volunteering, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c1613d210d494784b469f5190f665462-finance-administration-officer-coordinating-committee-for-international-voluntary-service-budapest</t>
+  </si>
+  <si>
+    <t>Grant Development &amp; Capital Campaign Consultant: Help build the future of education in the Bay Islands. BIIS is seeking an experienced fundraising professional to help secure major philanthropic funding for a expanding PreK–12 school campus in Roatán, Honduras.</t>
+  </si>
+  <si>
+    <t>Bay Islands International School</t>
+  </si>
+  <si>
+    <t>USD 50.00 - 90.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/560c268e69e44f90a5a0e017de8bee2a-grant-development-capital-campaign-consultant-help-build-the-future-of-education-in-the-bay-islands-biis-is-seeking-an-experienced-fundraising-professional-to-help-secure-major-philanthropic-funding-for-a-expanding-prek12-school-campus-in-roatan-honduras-bay-islands-international-school-roatan</t>
+  </si>
+  <si>
+    <t>Grants Manager 2 Position</t>
+  </si>
+  <si>
+    <t>Boys &amp; Girls Club of Dane County</t>
+  </si>
+  <si>
+    <t>Fitchburg, Wisconsin</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 52000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c6b37a07609b4a04be47ff8cb39160a9-grants-manager-2-position-boys-girls-club-of-dane-county-fitchburg</t>
+  </si>
+  <si>
+    <t>Head Veterinarian - Work in the Bolivian Jungle with rescued wildlife</t>
+  </si>
+  <si>
+    <t>Comunidad Inti Wara Yassi (CIWY)</t>
+  </si>
+  <si>
+    <t>San Buenaventura, La Paz, BO</t>
+  </si>
+  <si>
+    <t>BOB 2500.00/month</t>
+  </si>
+  <si>
+    <t>Climate Change, Rural Areas, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ae872096f7fa48d6a8970c709a8eb227-head-veterinarian-work-in-the-bolivian-jungle-with-rescued-wildlife-comunidad-inti-wara-yassi-ciwy-san-buenaventura</t>
+  </si>
+  <si>
+    <t>Helpline Advocate</t>
+  </si>
+  <si>
+    <t>Massachusetts Advocates for Children</t>
+  </si>
+  <si>
+    <t>USD 45500.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bdd6816457c4417f8aabbb1ac23316ac-helpline-advocate-massachusetts-advocates-for-children-boston</t>
+  </si>
+  <si>
+    <t>High School SAT Teacher</t>
+  </si>
+  <si>
+    <t>Success Academy Charter Schools</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/da859246f59a4dd382251ab8c799c3a0-high-school-sat-teacher-success-academy-charter-schools-new-york</t>
+  </si>
+  <si>
+    <t>Housing Justice Community Organizer</t>
+  </si>
+  <si>
+    <t>Northwest Bronx Community &amp; Clergy Coalition</t>
+  </si>
+  <si>
+    <t>Bronx County, New York</t>
+  </si>
+  <si>
+    <t>USD 50480.00 - 56089.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1bd850995b0d406e83b3d2e8d89fc6fd-housing-justice-community-organizer-northwest-bronx-community-clergy-coalition-bronx-county</t>
+  </si>
+  <si>
+    <t>HS Math Teacher</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4affb0d1c98f43c5b38b8ed6001e8084-hs-math-teacher-success-academy-charter-schools-new-york</t>
+  </si>
+  <si>
+    <t>Human Resources Director</t>
+  </si>
+  <si>
+    <t>New York State Nurses Association</t>
+  </si>
+  <si>
+    <t>USD 190000.00 - 200000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/77f6826e1cec4236876700d820e8f822-human-resources-director-new-york-state-nurses-association-new-york</t>
+  </si>
+  <si>
+    <t>IDA Program Director</t>
+  </si>
+  <si>
+    <t>Neighborhood Partnerships</t>
+  </si>
+  <si>
+    <t>Portland, OR</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/20187d8a1e9641298118b759dfefd215-ida-program-director-neighborhood-partnerships-portland</t>
+  </si>
+  <si>
+    <t>Immigration Attorney (Padilla), Criminal Defense Practice</t>
+  </si>
+  <si>
+    <t>Brooklyn, NY</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 109000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1d69142587e942cfb8ff180b45e602e4-immigration-attorney-padilla-criminal-defense-practice-brooklyn-defender-services-brooklyn</t>
+  </si>
+  <si>
+    <t>Immigration Staff Attorney</t>
+  </si>
+  <si>
+    <t>Urban Justice Center - Domestic Violence Project</t>
+  </si>
+  <si>
+    <t>USD 73950.00 - 81714.56/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8d547c616800480a9b3309755028dd86-immigration-staff-attorney-urban-justice-center-domestic-violence-project-new-york</t>
+  </si>
+  <si>
+    <t>Institutional Grants Officer</t>
+  </si>
+  <si>
+    <t>Seva Foundation</t>
+  </si>
+  <si>
+    <t>Berkeley, California</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f8ed6fc2ca514970a6da8416c3c861fb-institutional-grants-officer-seva-foundation-berkeley</t>
+  </si>
+  <si>
+    <t>Interim Supervising Attorney: Housing Justice</t>
+  </si>
+  <si>
+    <t>TakeRoot Justice</t>
+  </si>
+  <si>
+    <t>USD 90990.00 - 104050.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c284c27194174e588d97a285a8d80369-interim-supervising-attorney-housing-justice-takeroot-justice-new-york</t>
+  </si>
+  <si>
+    <t>Justice in Public Safety Project Counsel</t>
+  </si>
+  <si>
+    <t>NAACP Legal Defense and Educational Fund, Inc.</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ea5130d7c70e483e95864771199cc86b-justice-in-public-safety-project-counsel-naacp-legal-defense-and-educational-fund-inc-washington</t>
+  </si>
+  <si>
+    <t>Atlanta, Georgia</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c19def50a3f14b89a12a6cdb6ce12614-justice-in-public-safety-project-counsel-naacp-legal-defense-and-educational-fund-inc-atlanta</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/40f9387a47ff43a28ab791645f4f600e-justice-in-public-safety-project-counsel-naacp-legal-defense-and-educational-fund-inc-new-york</t>
+  </si>
+  <si>
+    <t>Learning Content Manager, SAGECare</t>
+  </si>
+  <si>
+    <t>SAGE | Advocacy and Services for LGBT Elders, Inc.</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Housing Homelessness, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/383855caabbc4cfaab41467a9a750633-learning-content-manager-sagecare-sage-advocacy-and-services-for-lgbt-elders-inc-new-york</t>
+  </si>
+  <si>
+    <t>Legal Assistant, Criminal Practice</t>
+  </si>
+  <si>
+    <t>Jamaica, NY</t>
+  </si>
+  <si>
+    <t>USD 69000.00 - 74000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7b3cc0207f96442fb9d3c2aa02d420e8-legal-assistant-criminal-practice-brooklyn-defender-services-jamaica</t>
+  </si>
+  <si>
+    <t>Líder de proyecto en CDMX - Edo. Mex</t>
+  </si>
+  <si>
+    <t>Ciudad de México, Ciudad de México, MX</t>
+  </si>
+  <si>
+    <t>MXN 17850.00 - 17850.00/month</t>
+  </si>
+  <si>
+    <t>Education, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/448dfef9b25340eba1ca5c42960d659c-lider-de-proyecto-en-cdmx-edo-mex-educacion-para-compartir-mexico-ciudad-de-mexico</t>
+  </si>
+  <si>
+    <t>Loevy + Loevy Summer Associates</t>
+  </si>
+  <si>
+    <t>Loevy + Loevy</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Transparency Oversight, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/9974162ee51d483caadbc9c383bfb851-loevy-loevy-summer-associates-loevy-loevy-chicago</t>
+  </si>
+  <si>
+    <t>Major Gifts Officer</t>
+  </si>
+  <si>
+    <t>New York Civil Liberties Union Foundation</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/3979fdc410984f808a49bb814624c196-major-gifts-officer-new-york-civil-liberties-union-foundation-new-york</t>
+  </si>
+  <si>
+    <t>Middle School Math Teachers</t>
+  </si>
+  <si>
+    <t>Wissahickon Charter School</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9282ec97922a4394bb9b36010ca7bfd8-middle-school-math-teachers-wissahickon-charter-school-philadelphia</t>
+  </si>
+  <si>
+    <t>Minister of Children, Youth, and Families</t>
+  </si>
+  <si>
+    <t>Bear Creek Christian Church</t>
+  </si>
+  <si>
+    <t>Colorado Springs, Colorado</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 67000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7a4a65367a604f3080d0d0c7e278a6c5-minister-of-children-youth-and-families-bear-creek-christian-church-colorado-springs</t>
+  </si>
+  <si>
+    <t>Mo P&amp;A Executive Director</t>
+  </si>
+  <si>
+    <t>Missouri Protection &amp; Advocacy Services</t>
+  </si>
+  <si>
+    <t>Jefferson City, Missouri</t>
+  </si>
+  <si>
+    <t>Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/183089880ac1438190f515361e039199-mo-pa-executive-director-missouri-protection-advocacy-services-jefferson-city</t>
+  </si>
+  <si>
+    <t>MST Family Therapist</t>
+  </si>
+  <si>
+    <t>Youth Villages</t>
+  </si>
+  <si>
+    <t>Memphis, Tennessee</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/093035a2646144adb51ee21116c658c2-mst-family-therapist-youth-villages-memphis</t>
+  </si>
+  <si>
+    <t>Network Development &amp; National Initiatives Director</t>
+  </si>
+  <si>
+    <t>Council on American-Islamic Relations - National Headquarters</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 116000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cf9b5ecd5a4a4e45aa4e6adebc256373-network-development-national-initiatives-director-council-on-american-islamic-relations-national-headquarters-washington</t>
+  </si>
+  <si>
+    <t>NY Middle School Math Teacher SY26-27</t>
+  </si>
+  <si>
+    <t>Excellence Community Schools</t>
+  </si>
+  <si>
+    <t>Bronx, NY</t>
+  </si>
+  <si>
+    <t>USD 60271.00 - 148412.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6d55ba404a984bc5b6c5d9fa8c18dc90-ny-middle-school-math-teacher-sy26-27-excellence-community-schools-bronx</t>
+  </si>
+  <si>
+    <t>NY Middle School Science Teacher SY26-27</t>
+  </si>
+  <si>
+    <t>Bronx, New York</t>
+  </si>
+  <si>
+    <t>USD 60271.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0b9e9fdabef14b0aaf33aa28cad02606-ny-middle-school-science-teacher-sy26-27-excellence-community-schools-bronx</t>
+  </si>
+  <si>
+    <t>Office Coordinator (Secretariat Office)</t>
+  </si>
+  <si>
+    <t>Maryknoll Sisters</t>
+  </si>
+  <si>
+    <t>Ossining, New York</t>
+  </si>
+  <si>
+    <t>USD 54080.00 - 54080.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Climate Change, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8c2c9da9f21c4f8e809b1998361a332c-office-coordinator-secretariat-office-maryknoll-sisters-ossining</t>
+  </si>
+  <si>
+    <t>Operations Administrative Assistant</t>
+  </si>
+  <si>
+    <t>Paul Angell Foundation</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/496acc0438a643a9b7e1f75937ca8b85-operations-administrative-assistant-paul-angell-foundation-chicago</t>
+  </si>
+  <si>
+    <t>Operations, HR &amp; Development Manager</t>
+  </si>
+  <si>
+    <t>Baker Institute for Children with Hearing Loss</t>
+  </si>
+  <si>
+    <t>USD 40.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Communications Access, Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ef34bf9192624d48aecdd18250a93a18-operations-hr-development-manager-baker-institute-for-children-with-hearing-loss-palo-alto</t>
+  </si>
+  <si>
+    <t>Paralegal (Client Advocate) - Prison Based Services</t>
+  </si>
+  <si>
+    <t>Appellate Advocates</t>
+  </si>
+  <si>
+    <t>USD 64375.00 - 94701.09/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3885f5cc661a40aeb93104aba0b7039e-paralegal-client-advocate-prison-based-services-appellate-advocates-new-york</t>
+  </si>
+  <si>
+    <t>Part-time Math Instructional Coach serving Entering and Emerging Multilingual Learners - 19 hours weekly (2.5 days)</t>
+  </si>
+  <si>
+    <t>Bridges to Academic Success</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 40.00 - 50.00/hour</t>
+  </si>
+  <si>
+    <t>Education, Children Youth, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/20b901ae6a534392afc249c9a9e0dc16-part-time-math-instructional-coach-serving-entering-and-emerging-multilingual-learners-19-hours-weekly-25-days-bridges-to-academic-success-new-york</t>
+  </si>
+  <si>
+    <t>Part-Time: Human Resources Specialist</t>
+  </si>
+  <si>
+    <t>Pawsperity</t>
+  </si>
+  <si>
+    <t>Kansas City, Missouri</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Animals, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/de34071b5e7b47aebd1af75924744b7e-part-time-human-resources-specialist-pawsperity-kansas-city</t>
+  </si>
+  <si>
+    <t>President, ROC USA Capital</t>
+  </si>
+  <si>
+    <t>ROC USA</t>
+  </si>
+  <si>
+    <t>USD 230000.00 - 270000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Rural Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f880a46faf0e4590a2510e06c6a5aed2-president-roc-usa-capital-roc-usa-washington</t>
+  </si>
+  <si>
+    <t>Product &amp; Portfolio Director (Full-Time Position, Hybrid)</t>
+  </si>
+  <si>
+    <t>Cause Strategy Partners</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/9071ec029b7747bf8642c5c28fece046-product-portfolio-director-full-time-position-hybrid-cause-strategy-partners-new-york</t>
+  </si>
+  <si>
+    <t>Program Assistant - Conservation</t>
+  </si>
+  <si>
+    <t>The Wyss Foundation</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Philanthropy, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d38d820622ba4374bc7f96dc6099eb3f-program-assistant-conservation-the-wyss-foundation-washington</t>
+  </si>
+  <si>
+    <t>Recruiter (Part-time, Temporary)</t>
+  </si>
+  <si>
+    <t>Columbia University, Office of Alumni Relations and Development</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 40000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/358211387aae4d3287d2e39aa0f085f1-recruiter-part-time-temporary-columbia-university-office-of-alumni-relations-and-development-new-york</t>
+  </si>
+  <si>
+    <t>Regional Campaign Manager, Northern California</t>
+  </si>
+  <si>
+    <t>Greenlight America</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9a4cd646906b45ddad4bf16e933e8997-regional-campaign-manager-northern-california-greenlight-america-washington</t>
+  </si>
+  <si>
+    <t>Sales Associate</t>
+  </si>
+  <si>
+    <t>Mercado Global</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fe50a40fd8bd413aafc608e3ad606de2-sales-associate-mercado-global-brooklyn</t>
+  </si>
+  <si>
+    <t>Remote (GT)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c258d13c70f54c308f2e05ac606be756-sales-associate-mercado-global-brooklyn</t>
+  </si>
+  <si>
+    <t>Senior Attorney (Litigation)</t>
+  </si>
+  <si>
+    <t>New York City School Construction Authority</t>
+  </si>
+  <si>
+    <t>Queens County, New York</t>
+  </si>
+  <si>
+    <t>USD 91193.00 - 155274.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1d5f1049445741369a67966620d8b8a5-senior-attorney-litigation-new-york-city-school-construction-authority-queens-county</t>
+  </si>
+  <si>
+    <t>Senior Attorney or Counsel</t>
+  </si>
+  <si>
+    <t>Lambda Legal</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/05f20beba07f4eee8f6ab837f33c0713-senior-attorney-or-counsel-lambda-legal-chicago</t>
+  </si>
+  <si>
+    <t>Senior Communications Associate</t>
+  </si>
+  <si>
+    <t>The Annie E. Casey Foundation</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>Children Youth, Economic Development, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/50c97a5eb6f247c884cbb7cdf40b4f0b-senior-communications-associate-the-annie-e-casey-foundation-baltimore</t>
+  </si>
+  <si>
+    <t>Senior Director of Development</t>
+  </si>
+  <si>
+    <t>EMPath</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Poverty, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7b53023ab0fe40358253f7af54a81a98-senior-director-of-development-empath-boston</t>
+  </si>
+  <si>
+    <t>Senior Immigrant Rights Attorney</t>
+  </si>
+  <si>
+    <t>Legal Aid Justice Center</t>
+  </si>
+  <si>
+    <t>Norfolk, Virginia</t>
+  </si>
+  <si>
+    <t>USD 76521.70 - 102462.56/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Poverty, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f1068fd9978c4d1ea248a428c7a8aead-senior-immigrant-rights-attorney-legal-aid-justice-center-norfolk</t>
+  </si>
+  <si>
+    <t>Shipper / Receiver</t>
+  </si>
+  <si>
+    <t>Mansfield, Massachusetts</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c00046b8cef14b1fbdcb34621335c266-shipper-receiver-community-servings-inc-mansfield</t>
+  </si>
+  <si>
+    <t>Social Worker Program Administrator</t>
+  </si>
+  <si>
+    <t>Fifth Avenue Presbyterian Church</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Hunger Food Security, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e9bb8c0a155143cda3ced44e25547457-social-worker-program-administrator-fifth-avenue-presbyterian-church-new-york</t>
+  </si>
+  <si>
+    <t>Staff Accountant</t>
+  </si>
+  <si>
+    <t>ReSurge International</t>
+  </si>
+  <si>
+    <t>Sunnyvale, California</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3f68e129919e4cfc8a9f5778e4136a11-staff-accountant-resurge-international-sunnyvale</t>
+  </si>
+  <si>
+    <t>Staff Attorney-Housing Unit</t>
+  </si>
+  <si>
+    <t>District Council 37, Health &amp; Security Plan</t>
+  </si>
+  <si>
+    <t>USD 73270.00 - 104637.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace, Conflict Resolution, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1b214a169e664bc3892c1feaa900c830-staff-attorney-housing-unit-district-council-37-health-security-plan-new-york</t>
+  </si>
+  <si>
+    <t>Staff Attorney-MELS Matrimonial Unit</t>
+  </si>
+  <si>
+    <t>Family, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/037860e50b5f4555906456ef187c051e-staff-attorney-mels-matrimonial-unit-district-council-37-health-security-plan-new-york</t>
+  </si>
+  <si>
+    <t>Staff Attorney, New York Family Unity Project (NYIFUP)</t>
+  </si>
+  <si>
+    <t>New York Legal Assistance Group (NYLAG)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a8203a39170b4d4db5cb46139fd9cb69-staff-attorney-new-york-family-unity-project-nyifup-new-york-legal-assistance-group-nylag-new-york</t>
+  </si>
+  <si>
+    <t>Strategic Planning Consultant</t>
+  </si>
+  <si>
+    <t>Maya Health Alliance | Wuqu' Kawoq</t>
+  </si>
+  <si>
+    <t>Antigua Guatemala, Sacatepéquez, GT</t>
+  </si>
+  <si>
+    <t>Health Medicine, Human Rights Civil Liberties, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c081dae2faaa4d61a07fe21cc2d3c97f-strategic-planning-consultant-maya-health-alliance-wuqu-kawoq-antigua-guatemala</t>
+  </si>
+  <si>
+    <t>Student Advisor</t>
+  </si>
+  <si>
+    <t>East Side House Settlement</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/63a2b06e04d94de5bdc2d9f4f09fd0a4-student-advisor-east-side-house-settlement-bronx-county</t>
+  </si>
+  <si>
+    <t>Temporary Staff Attorney - Immigration Law Project</t>
+  </si>
+  <si>
+    <t>Mobilization for Justice</t>
+  </si>
+  <si>
+    <t>USD 93567.35 - 141629.79/year</t>
+  </si>
+  <si>
+    <t>Family, Job Workplace, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7c0ee4af36c94bac8dfc8dafa5adcba2-temporary-staff-attorney-immigration-law-project-mobilization-for-justice-new-york</t>
+  </si>
+  <si>
+    <t>Trial Attorney</t>
+  </si>
+  <si>
+    <t>Remote (Washington, District of Columbia)</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1e40bfcff960432980b15a145582d850-trial-attorney-council-on-american-islamic-relations-national-headquarters-washington</t>
+  </si>
+  <si>
+    <t>Veterinario Principal - trabajar con la fauna silvestre en la selva boliviana</t>
+  </si>
+  <si>
+    <t>San Buenaventura, San Buenaventura, BO</t>
+  </si>
+  <si>
+    <t>Animals, Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f3a3ed7d02c24c2c98f9a7ffa6a725be-veterinario-principal-trabajar-con-la-fauna-silvestre-en-la-selva-boliviana-comunidad-inti-wara-yassi-ciwy-san-buenaventura</t>
+  </si>
+  <si>
+    <t>Vice President of Programs</t>
+  </si>
+  <si>
+    <t>JoyRx | Children's Cancer Association</t>
+  </si>
+  <si>
+    <t>USD 125000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Health Medicine, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/96038b11f6a64caf93856afa536643e3-vice-president-of-programs-joyrx-childrens-cancer-association-portland</t>
+  </si>
+  <si>
+    <t>Volunteer Coordinator</t>
+  </si>
+  <si>
+    <t>Civic Bridgers</t>
+  </si>
+  <si>
+    <t>Saint Paul, Minnesota</t>
+  </si>
+  <si>
+    <t>USD 960.07 - 960.07/week</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5faada291b7a409187fe18e04318b1c2-volunteer-coordinator-civic-bridgers-saint-paul</t>
+  </si>
+  <si>
+    <t>The Mountaineers</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>USD 22.14 - 24.04/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Sports Recreation, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3d9b0610744a4c1b874b8ee24332f283-volunteer-coordinator-the-mountaineers-seattle</t>
+  </si>
+  <si>
+    <t>Youth Engagement Coordinator</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7f15c209a17540ef82fcc26d1bd73b8b-youth-engagement-coordinator-civic-bridgers-saint-paul</t>
+  </si>
+  <si>
+    <t>Youth Outreach Associate</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/522ae96f76474661b5744730e6c45c81-youth-outreach-associate-civic-bridgers-saint-paul</t>
   </si>
 </sst>
 </file>
@@ -498,7 +2589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -617,16 +2708,844 @@
         <v>29</v>
       </c>
       <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
         <v>11</v>
       </c>
-      <c r="E5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" s="2" t="s">
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" t="s">
+        <v>62</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" t="s">
+        <v>70</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" t="s">
+        <v>80</v>
+      </c>
+      <c r="E14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>87</v>
+      </c>
+      <c r="F15" t="s">
         <v>32</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>92</v>
+      </c>
+      <c r="F16" t="s">
+        <v>93</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>97</v>
+      </c>
+      <c r="F17" t="s">
+        <v>98</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>102</v>
+      </c>
+      <c r="F18" t="s">
+        <v>103</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>105</v>
+      </c>
+      <c r="B19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" t="s">
+        <v>60</v>
+      </c>
+      <c r="E19" t="s">
+        <v>108</v>
+      </c>
+      <c r="F19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" t="s">
+        <v>112</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>113</v>
+      </c>
+      <c r="F20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" t="s">
+        <v>116</v>
+      </c>
+      <c r="C21" t="s">
+        <v>117</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>118</v>
+      </c>
+      <c r="F21" t="s">
+        <v>119</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="s">
+        <v>122</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>123</v>
+      </c>
+      <c r="F22" t="s">
+        <v>124</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" t="s">
+        <v>128</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>129</v>
+      </c>
+      <c r="F23" t="s">
+        <v>130</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>132</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>133</v>
+      </c>
+      <c r="F24" t="s">
+        <v>134</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>136</v>
+      </c>
+      <c r="B25" t="s">
+        <v>137</v>
+      </c>
+      <c r="C25" t="s">
+        <v>138</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>139</v>
+      </c>
+      <c r="F25" t="s">
+        <v>140</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>142</v>
+      </c>
+      <c r="B26" t="s">
+        <v>143</v>
+      </c>
+      <c r="C26" t="s">
+        <v>144</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>145</v>
+      </c>
+      <c r="F26" t="s">
+        <v>119</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>147</v>
+      </c>
+      <c r="B27" t="s">
+        <v>148</v>
+      </c>
+      <c r="C27" t="s">
+        <v>149</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>150</v>
+      </c>
+      <c r="F27" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>152</v>
+      </c>
+      <c r="B28" t="s">
+        <v>148</v>
+      </c>
+      <c r="C28" t="s">
+        <v>149</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>153</v>
+      </c>
+      <c r="F28" t="s">
+        <v>19</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>155</v>
+      </c>
+      <c r="B29" t="s">
+        <v>156</v>
+      </c>
+      <c r="C29" t="s">
+        <v>157</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>158</v>
+      </c>
+      <c r="F29" t="s">
+        <v>32</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>160</v>
+      </c>
+      <c r="B30" t="s">
+        <v>161</v>
+      </c>
+      <c r="C30" t="s">
+        <v>162</v>
+      </c>
+      <c r="D30" t="s">
+        <v>60</v>
+      </c>
+      <c r="E30" t="s">
+        <v>163</v>
+      </c>
+      <c r="F30" t="s">
+        <v>119</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>165</v>
+      </c>
+      <c r="B31" t="s">
+        <v>166</v>
+      </c>
+      <c r="C31" t="s">
+        <v>167</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
+        <v>168</v>
+      </c>
+      <c r="F31" t="s">
+        <v>169</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>171</v>
+      </c>
+      <c r="B32" t="s">
+        <v>172</v>
+      </c>
+      <c r="C32" t="s">
+        <v>173</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>174</v>
+      </c>
+      <c r="F32" t="s">
+        <v>175</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>177</v>
+      </c>
+      <c r="B33" t="s">
+        <v>178</v>
+      </c>
+      <c r="C33" t="s">
+        <v>179</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>180</v>
+      </c>
+      <c r="F33" t="s">
+        <v>181</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>183</v>
+      </c>
+      <c r="B34" t="s">
+        <v>184</v>
+      </c>
+      <c r="C34" t="s">
+        <v>185</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>186</v>
+      </c>
+      <c r="F34" t="s">
+        <v>55</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>188</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="s">
+        <v>122</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>18</v>
+      </c>
+      <c r="F35" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>190</v>
+      </c>
+      <c r="B36" t="s">
+        <v>191</v>
+      </c>
+      <c r="C36" t="s">
+        <v>192</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>193</v>
+      </c>
+      <c r="F36" t="s">
+        <v>194</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>196</v>
+      </c>
+      <c r="B37" t="s">
+        <v>184</v>
+      </c>
+      <c r="C37" t="s">
+        <v>185</v>
+      </c>
+      <c r="D37" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>197</v>
+      </c>
+      <c r="F37" t="s">
+        <v>55</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>199</v>
+      </c>
+      <c r="B38" t="s">
+        <v>200</v>
+      </c>
+      <c r="C38" t="s">
+        <v>201</v>
+      </c>
+      <c r="D38" t="s">
+        <v>60</v>
+      </c>
+      <c r="E38" t="s">
+        <v>202</v>
+      </c>
+      <c r="F38" t="s">
+        <v>32</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>204</v>
+      </c>
+      <c r="B39" t="s">
+        <v>205</v>
+      </c>
+      <c r="C39" t="s">
+        <v>206</v>
+      </c>
+      <c r="D39" t="s">
+        <v>60</v>
+      </c>
+      <c r="E39" t="s">
+        <v>207</v>
+      </c>
+      <c r="F39" t="s">
+        <v>32</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>209</v>
+      </c>
+      <c r="B40" t="s">
+        <v>210</v>
+      </c>
+      <c r="C40" t="s">
+        <v>211</v>
+      </c>
+      <c r="D40" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" t="s">
+        <v>212</v>
+      </c>
+      <c r="F40" t="s">
+        <v>38</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>214</v>
+      </c>
+      <c r="B41" t="s">
+        <v>215</v>
+      </c>
+      <c r="C41" t="s">
+        <v>216</v>
+      </c>
+      <c r="D41" t="s">
+        <v>60</v>
+      </c>
+      <c r="E41" t="s">
+        <v>217</v>
+      </c>
+      <c r="F41" t="s">
+        <v>218</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -636,6 +3555,42 @@
     <hyperlink ref="H3" r:id="rId2"/>
     <hyperlink ref="H4" r:id="rId3"/>
     <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -644,7 +3599,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -683,8 +3638,58 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F2" t="s">
+        <v>225</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E3" t="s">
+        <v>230</v>
+      </c>
+      <c r="F3" t="s">
+        <v>231</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -692,7 +3697,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H103"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -731,8 +3736,2458 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F2" t="s">
+        <v>238</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D3" t="s">
+        <v>236</v>
+      </c>
+      <c r="E3" t="s">
+        <v>243</v>
+      </c>
+      <c r="F3" t="s">
+        <v>244</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C4" t="s">
+        <v>248</v>
+      </c>
+      <c r="D4" t="s">
+        <v>236</v>
+      </c>
+      <c r="E4" t="s">
+        <v>249</v>
+      </c>
+      <c r="F4" t="s">
+        <v>250</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B5" t="s">
+        <v>253</v>
+      </c>
+      <c r="C5" t="s">
+        <v>254</v>
+      </c>
+      <c r="D5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E5" t="s">
+        <v>255</v>
+      </c>
+      <c r="F5" t="s">
+        <v>256</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>258</v>
+      </c>
+      <c r="B6" t="s">
+        <v>259</v>
+      </c>
+      <c r="C6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D6" t="s">
+        <v>236</v>
+      </c>
+      <c r="E6" t="s">
+        <v>261</v>
+      </c>
+      <c r="F6" t="s">
+        <v>262</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>264</v>
+      </c>
+      <c r="B7" t="s">
+        <v>265</v>
+      </c>
+      <c r="C7" t="s">
+        <v>254</v>
+      </c>
+      <c r="D7" t="s">
+        <v>236</v>
+      </c>
+      <c r="E7" t="s">
+        <v>266</v>
+      </c>
+      <c r="F7" t="s">
+        <v>267</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>269</v>
+      </c>
+      <c r="B8" t="s">
+        <v>270</v>
+      </c>
+      <c r="C8" t="s">
+        <v>271</v>
+      </c>
+      <c r="D8" t="s">
+        <v>236</v>
+      </c>
+      <c r="E8" t="s">
+        <v>272</v>
+      </c>
+      <c r="F8" t="s">
+        <v>273</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>275</v>
+      </c>
+      <c r="B9" t="s">
+        <v>276</v>
+      </c>
+      <c r="C9" t="s">
+        <v>277</v>
+      </c>
+      <c r="D9" t="s">
+        <v>236</v>
+      </c>
+      <c r="E9" t="s">
+        <v>266</v>
+      </c>
+      <c r="F9" t="s">
+        <v>278</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>280</v>
+      </c>
+      <c r="B10" t="s">
+        <v>281</v>
+      </c>
+      <c r="C10" t="s">
+        <v>282</v>
+      </c>
+      <c r="D10" t="s">
+        <v>236</v>
+      </c>
+      <c r="E10" t="s">
+        <v>283</v>
+      </c>
+      <c r="F10" t="s">
+        <v>284</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>286</v>
+      </c>
+      <c r="B11" t="s">
+        <v>287</v>
+      </c>
+      <c r="C11" t="s">
+        <v>288</v>
+      </c>
+      <c r="D11" t="s">
+        <v>236</v>
+      </c>
+      <c r="E11" t="s">
+        <v>289</v>
+      </c>
+      <c r="F11" t="s">
+        <v>290</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>292</v>
+      </c>
+      <c r="B12" t="s">
+        <v>293</v>
+      </c>
+      <c r="C12" t="s">
+        <v>294</v>
+      </c>
+      <c r="D12" t="s">
+        <v>236</v>
+      </c>
+      <c r="E12" t="s">
+        <v>295</v>
+      </c>
+      <c r="F12" t="s">
+        <v>296</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>298</v>
+      </c>
+      <c r="B13" t="s">
+        <v>299</v>
+      </c>
+      <c r="C13" t="s">
+        <v>300</v>
+      </c>
+      <c r="D13" t="s">
+        <v>236</v>
+      </c>
+      <c r="E13" t="s">
+        <v>301</v>
+      </c>
+      <c r="F13" t="s">
+        <v>302</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>304</v>
+      </c>
+      <c r="B14" t="s">
+        <v>305</v>
+      </c>
+      <c r="C14" t="s">
+        <v>306</v>
+      </c>
+      <c r="D14" t="s">
+        <v>236</v>
+      </c>
+      <c r="E14" t="s">
+        <v>307</v>
+      </c>
+      <c r="F14" t="s">
+        <v>308</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>310</v>
+      </c>
+      <c r="B15" t="s">
+        <v>311</v>
+      </c>
+      <c r="C15" t="s">
+        <v>312</v>
+      </c>
+      <c r="D15" t="s">
+        <v>236</v>
+      </c>
+      <c r="E15" t="s">
+        <v>313</v>
+      </c>
+      <c r="F15" t="s">
+        <v>314</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>316</v>
+      </c>
+      <c r="B16" t="s">
+        <v>317</v>
+      </c>
+      <c r="C16" t="s">
+        <v>282</v>
+      </c>
+      <c r="D16" t="s">
+        <v>236</v>
+      </c>
+      <c r="E16" t="s">
+        <v>318</v>
+      </c>
+      <c r="F16" t="s">
+        <v>319</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>321</v>
+      </c>
+      <c r="B17" t="s">
+        <v>322</v>
+      </c>
+      <c r="C17" t="s">
+        <v>323</v>
+      </c>
+      <c r="D17" t="s">
+        <v>236</v>
+      </c>
+      <c r="E17" t="s">
+        <v>324</v>
+      </c>
+      <c r="F17" t="s">
+        <v>325</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>327</v>
+      </c>
+      <c r="B18" t="s">
+        <v>328</v>
+      </c>
+      <c r="C18" t="s">
+        <v>254</v>
+      </c>
+      <c r="D18" t="s">
+        <v>236</v>
+      </c>
+      <c r="E18" t="s">
+        <v>329</v>
+      </c>
+      <c r="F18" t="s">
+        <v>330</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>332</v>
+      </c>
+      <c r="B19" t="s">
+        <v>333</v>
+      </c>
+      <c r="C19" t="s">
+        <v>334</v>
+      </c>
+      <c r="D19" t="s">
+        <v>335</v>
+      </c>
+      <c r="E19" t="s">
+        <v>336</v>
+      </c>
+      <c r="F19" t="s">
+        <v>337</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>339</v>
+      </c>
+      <c r="B20" t="s">
+        <v>340</v>
+      </c>
+      <c r="C20" t="s">
+        <v>341</v>
+      </c>
+      <c r="D20" t="s">
+        <v>236</v>
+      </c>
+      <c r="E20" t="s">
+        <v>342</v>
+      </c>
+      <c r="F20" t="s">
+        <v>343</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>345</v>
+      </c>
+      <c r="B21" t="s">
+        <v>346</v>
+      </c>
+      <c r="C21" t="s">
+        <v>235</v>
+      </c>
+      <c r="D21" t="s">
+        <v>347</v>
+      </c>
+      <c r="E21" t="s">
+        <v>348</v>
+      </c>
+      <c r="F21" t="s">
+        <v>349</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>351</v>
+      </c>
+      <c r="B22" t="s">
+        <v>352</v>
+      </c>
+      <c r="C22" t="s">
+        <v>353</v>
+      </c>
+      <c r="D22" t="s">
+        <v>347</v>
+      </c>
+      <c r="E22" t="s">
+        <v>354</v>
+      </c>
+      <c r="F22" t="s">
+        <v>355</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>357</v>
+      </c>
+      <c r="B23" t="s">
+        <v>358</v>
+      </c>
+      <c r="C23" t="s">
+        <v>359</v>
+      </c>
+      <c r="D23" t="s">
+        <v>236</v>
+      </c>
+      <c r="E23" t="s">
+        <v>360</v>
+      </c>
+      <c r="F23" t="s">
+        <v>361</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>363</v>
+      </c>
+      <c r="B24" t="s">
+        <v>364</v>
+      </c>
+      <c r="C24" t="s">
+        <v>306</v>
+      </c>
+      <c r="D24" t="s">
+        <v>236</v>
+      </c>
+      <c r="E24" t="s">
+        <v>365</v>
+      </c>
+      <c r="F24" t="s">
+        <v>366</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>368</v>
+      </c>
+      <c r="B25" t="s">
+        <v>369</v>
+      </c>
+      <c r="C25" t="s">
+        <v>235</v>
+      </c>
+      <c r="D25" t="s">
+        <v>236</v>
+      </c>
+      <c r="E25" t="s">
+        <v>370</v>
+      </c>
+      <c r="F25" t="s">
+        <v>371</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>373</v>
+      </c>
+      <c r="B26" t="s">
+        <v>374</v>
+      </c>
+      <c r="C26" t="s">
+        <v>323</v>
+      </c>
+      <c r="D26" t="s">
+        <v>236</v>
+      </c>
+      <c r="E26" t="s">
+        <v>375</v>
+      </c>
+      <c r="F26" t="s">
+        <v>376</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>378</v>
+      </c>
+      <c r="B27" t="s">
+        <v>379</v>
+      </c>
+      <c r="C27" t="s">
+        <v>254</v>
+      </c>
+      <c r="D27" t="s">
+        <v>236</v>
+      </c>
+      <c r="E27" t="s">
+        <v>380</v>
+      </c>
+      <c r="F27" t="s">
+        <v>278</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>382</v>
+      </c>
+      <c r="B28" t="s">
+        <v>383</v>
+      </c>
+      <c r="C28" t="s">
+        <v>384</v>
+      </c>
+      <c r="D28" t="s">
+        <v>236</v>
+      </c>
+      <c r="E28" t="s">
+        <v>385</v>
+      </c>
+      <c r="F28" t="s">
+        <v>386</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>388</v>
+      </c>
+      <c r="B29" t="s">
+        <v>389</v>
+      </c>
+      <c r="C29" t="s">
+        <v>390</v>
+      </c>
+      <c r="D29" t="s">
+        <v>236</v>
+      </c>
+      <c r="E29" t="s">
+        <v>391</v>
+      </c>
+      <c r="F29" t="s">
+        <v>392</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>394</v>
+      </c>
+      <c r="B30" t="s">
+        <v>358</v>
+      </c>
+      <c r="C30" t="s">
+        <v>359</v>
+      </c>
+      <c r="D30" t="s">
+        <v>236</v>
+      </c>
+      <c r="E30" t="s">
+        <v>386</v>
+      </c>
+      <c r="F30" t="s">
+        <v>395</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>397</v>
+      </c>
+      <c r="B31" t="s">
+        <v>398</v>
+      </c>
+      <c r="C31" t="s">
+        <v>323</v>
+      </c>
+      <c r="D31" t="s">
+        <v>236</v>
+      </c>
+      <c r="E31" t="s">
+        <v>391</v>
+      </c>
+      <c r="F31" t="s">
+        <v>399</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>401</v>
+      </c>
+      <c r="B32" t="s">
+        <v>402</v>
+      </c>
+      <c r="C32" t="s">
+        <v>323</v>
+      </c>
+      <c r="D32" t="s">
+        <v>236</v>
+      </c>
+      <c r="E32" t="s">
+        <v>403</v>
+      </c>
+      <c r="F32" t="s">
+        <v>386</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>405</v>
+      </c>
+      <c r="B33" t="s">
+        <v>406</v>
+      </c>
+      <c r="C33" t="s">
+        <v>306</v>
+      </c>
+      <c r="D33" t="s">
+        <v>236</v>
+      </c>
+      <c r="E33" t="s">
+        <v>407</v>
+      </c>
+      <c r="F33" t="s">
+        <v>408</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>410</v>
+      </c>
+      <c r="B34" t="s">
+        <v>411</v>
+      </c>
+      <c r="C34" t="s">
+        <v>254</v>
+      </c>
+      <c r="D34" t="s">
+        <v>236</v>
+      </c>
+      <c r="E34" t="s">
+        <v>412</v>
+      </c>
+      <c r="F34" t="s">
+        <v>413</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>415</v>
+      </c>
+      <c r="B35" t="s">
+        <v>416</v>
+      </c>
+      <c r="C35" t="s">
+        <v>277</v>
+      </c>
+      <c r="D35" t="s">
+        <v>236</v>
+      </c>
+      <c r="E35" t="s">
+        <v>417</v>
+      </c>
+      <c r="F35" t="s">
+        <v>386</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>419</v>
+      </c>
+      <c r="B36" t="s">
+        <v>420</v>
+      </c>
+      <c r="C36" t="s">
+        <v>421</v>
+      </c>
+      <c r="D36" t="s">
+        <v>335</v>
+      </c>
+      <c r="E36" t="s">
+        <v>422</v>
+      </c>
+      <c r="F36" t="s">
+        <v>423</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>89</v>
+      </c>
+      <c r="B37" t="s">
+        <v>425</v>
+      </c>
+      <c r="C37" t="s">
+        <v>426</v>
+      </c>
+      <c r="D37" t="s">
+        <v>236</v>
+      </c>
+      <c r="E37" t="s">
+        <v>307</v>
+      </c>
+      <c r="F37" t="s">
+        <v>427</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>89</v>
+      </c>
+      <c r="B38" t="s">
+        <v>429</v>
+      </c>
+      <c r="C38" t="s">
+        <v>430</v>
+      </c>
+      <c r="D38" t="s">
+        <v>236</v>
+      </c>
+      <c r="E38" t="s">
+        <v>386</v>
+      </c>
+      <c r="F38" t="s">
+        <v>386</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>432</v>
+      </c>
+      <c r="B39" t="s">
+        <v>433</v>
+      </c>
+      <c r="C39" t="s">
+        <v>434</v>
+      </c>
+      <c r="D39" t="s">
+        <v>347</v>
+      </c>
+      <c r="E39" t="s">
+        <v>435</v>
+      </c>
+      <c r="F39" t="s">
+        <v>436</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>438</v>
+      </c>
+      <c r="B40" t="s">
+        <v>439</v>
+      </c>
+      <c r="C40" t="s">
+        <v>440</v>
+      </c>
+      <c r="D40" t="s">
+        <v>236</v>
+      </c>
+      <c r="E40" t="s">
+        <v>391</v>
+      </c>
+      <c r="F40" t="s">
+        <v>441</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>443</v>
+      </c>
+      <c r="B41" t="s">
+        <v>444</v>
+      </c>
+      <c r="C41" t="s">
+        <v>445</v>
+      </c>
+      <c r="D41" t="s">
+        <v>236</v>
+      </c>
+      <c r="E41" t="s">
+        <v>446</v>
+      </c>
+      <c r="F41" t="s">
+        <v>447</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>449</v>
+      </c>
+      <c r="B42" t="s">
+        <v>450</v>
+      </c>
+      <c r="C42" t="s">
+        <v>323</v>
+      </c>
+      <c r="D42" t="s">
+        <v>335</v>
+      </c>
+      <c r="E42" t="s">
+        <v>451</v>
+      </c>
+      <c r="F42" t="s">
+        <v>308</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>453</v>
+      </c>
+      <c r="B43" t="s">
+        <v>454</v>
+      </c>
+      <c r="C43" t="s">
+        <v>455</v>
+      </c>
+      <c r="D43" t="s">
+        <v>236</v>
+      </c>
+      <c r="E43" t="s">
+        <v>456</v>
+      </c>
+      <c r="F43" t="s">
+        <v>457</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>459</v>
+      </c>
+      <c r="B44" t="s">
+        <v>460</v>
+      </c>
+      <c r="C44" t="s">
+        <v>461</v>
+      </c>
+      <c r="D44" t="s">
+        <v>236</v>
+      </c>
+      <c r="E44" t="s">
+        <v>462</v>
+      </c>
+      <c r="F44" t="s">
+        <v>463</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>465</v>
+      </c>
+      <c r="B45" t="s">
+        <v>466</v>
+      </c>
+      <c r="C45" t="s">
+        <v>235</v>
+      </c>
+      <c r="D45" t="s">
+        <v>236</v>
+      </c>
+      <c r="E45" t="s">
+        <v>467</v>
+      </c>
+      <c r="F45" t="s">
+        <v>468</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>470</v>
+      </c>
+      <c r="B46" t="s">
+        <v>471</v>
+      </c>
+      <c r="C46" t="s">
+        <v>254</v>
+      </c>
+      <c r="D46" t="s">
+        <v>236</v>
+      </c>
+      <c r="E46" t="s">
+        <v>472</v>
+      </c>
+      <c r="F46" t="s">
+        <v>473</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>475</v>
+      </c>
+      <c r="B47" t="s">
+        <v>476</v>
+      </c>
+      <c r="C47" t="s">
+        <v>477</v>
+      </c>
+      <c r="D47" t="s">
+        <v>236</v>
+      </c>
+      <c r="E47" t="s">
+        <v>478</v>
+      </c>
+      <c r="F47" t="s">
+        <v>479</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>481</v>
+      </c>
+      <c r="B48" t="s">
+        <v>471</v>
+      </c>
+      <c r="C48" t="s">
+        <v>254</v>
+      </c>
+      <c r="D48" t="s">
+        <v>236</v>
+      </c>
+      <c r="E48" t="s">
+        <v>472</v>
+      </c>
+      <c r="F48" t="s">
+        <v>473</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>483</v>
+      </c>
+      <c r="B49" t="s">
+        <v>484</v>
+      </c>
+      <c r="C49" t="s">
+        <v>254</v>
+      </c>
+      <c r="D49" t="s">
+        <v>236</v>
+      </c>
+      <c r="E49" t="s">
+        <v>485</v>
+      </c>
+      <c r="F49" t="s">
+        <v>386</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>487</v>
+      </c>
+      <c r="B50" t="s">
+        <v>488</v>
+      </c>
+      <c r="C50" t="s">
+        <v>489</v>
+      </c>
+      <c r="D50" t="s">
+        <v>236</v>
+      </c>
+      <c r="E50" t="s">
+        <v>490</v>
+      </c>
+      <c r="F50" t="s">
+        <v>491</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>493</v>
+      </c>
+      <c r="B51" t="s">
+        <v>287</v>
+      </c>
+      <c r="C51" t="s">
+        <v>494</v>
+      </c>
+      <c r="D51" t="s">
+        <v>236</v>
+      </c>
+      <c r="E51" t="s">
+        <v>495</v>
+      </c>
+      <c r="F51" t="s">
+        <v>290</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>497</v>
+      </c>
+      <c r="B52" t="s">
+        <v>498</v>
+      </c>
+      <c r="C52" t="s">
+        <v>254</v>
+      </c>
+      <c r="D52" t="s">
+        <v>236</v>
+      </c>
+      <c r="E52" t="s">
+        <v>499</v>
+      </c>
+      <c r="F52" t="s">
+        <v>290</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>501</v>
+      </c>
+      <c r="B53" t="s">
+        <v>502</v>
+      </c>
+      <c r="C53" t="s">
+        <v>503</v>
+      </c>
+      <c r="D53" t="s">
+        <v>335</v>
+      </c>
+      <c r="E53" t="s">
+        <v>386</v>
+      </c>
+      <c r="F53" t="s">
+        <v>504</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>506</v>
+      </c>
+      <c r="B54" t="s">
+        <v>507</v>
+      </c>
+      <c r="C54" t="s">
+        <v>254</v>
+      </c>
+      <c r="D54" t="s">
+        <v>347</v>
+      </c>
+      <c r="E54" t="s">
+        <v>508</v>
+      </c>
+      <c r="F54" t="s">
+        <v>509</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>511</v>
+      </c>
+      <c r="B55" t="s">
+        <v>512</v>
+      </c>
+      <c r="C55" t="s">
+        <v>306</v>
+      </c>
+      <c r="D55" t="s">
+        <v>236</v>
+      </c>
+      <c r="E55" t="s">
+        <v>386</v>
+      </c>
+      <c r="F55" t="s">
+        <v>513</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>511</v>
+      </c>
+      <c r="B56" t="s">
+        <v>512</v>
+      </c>
+      <c r="C56" t="s">
+        <v>515</v>
+      </c>
+      <c r="D56" t="s">
+        <v>236</v>
+      </c>
+      <c r="E56" t="s">
+        <v>386</v>
+      </c>
+      <c r="F56" t="s">
+        <v>513</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>511</v>
+      </c>
+      <c r="B57" t="s">
+        <v>512</v>
+      </c>
+      <c r="C57" t="s">
+        <v>254</v>
+      </c>
+      <c r="D57" t="s">
+        <v>236</v>
+      </c>
+      <c r="E57" t="s">
+        <v>386</v>
+      </c>
+      <c r="F57" t="s">
+        <v>513</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>518</v>
+      </c>
+      <c r="B58" t="s">
+        <v>519</v>
+      </c>
+      <c r="C58" t="s">
+        <v>323</v>
+      </c>
+      <c r="D58" t="s">
+        <v>236</v>
+      </c>
+      <c r="E58" t="s">
+        <v>520</v>
+      </c>
+      <c r="F58" t="s">
+        <v>521</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>523</v>
+      </c>
+      <c r="B59" t="s">
+        <v>287</v>
+      </c>
+      <c r="C59" t="s">
+        <v>524</v>
+      </c>
+      <c r="D59" t="s">
+        <v>236</v>
+      </c>
+      <c r="E59" t="s">
+        <v>525</v>
+      </c>
+      <c r="F59" t="s">
+        <v>290</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>527</v>
+      </c>
+      <c r="B60" t="s">
+        <v>433</v>
+      </c>
+      <c r="C60" t="s">
+        <v>528</v>
+      </c>
+      <c r="D60" t="s">
+        <v>347</v>
+      </c>
+      <c r="E60" t="s">
+        <v>529</v>
+      </c>
+      <c r="F60" t="s">
+        <v>530</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>532</v>
+      </c>
+      <c r="B61" t="s">
+        <v>533</v>
+      </c>
+      <c r="C61" t="s">
+        <v>534</v>
+      </c>
+      <c r="D61" t="s">
+        <v>347</v>
+      </c>
+      <c r="E61" t="s">
+        <v>386</v>
+      </c>
+      <c r="F61" t="s">
+        <v>535</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>537</v>
+      </c>
+      <c r="B62" t="s">
+        <v>538</v>
+      </c>
+      <c r="C62" t="s">
+        <v>254</v>
+      </c>
+      <c r="D62" t="s">
+        <v>236</v>
+      </c>
+      <c r="E62" t="s">
+        <v>539</v>
+      </c>
+      <c r="F62" t="s">
+        <v>386</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>541</v>
+      </c>
+      <c r="B63" t="s">
+        <v>542</v>
+      </c>
+      <c r="C63" t="s">
+        <v>543</v>
+      </c>
+      <c r="D63" t="s">
+        <v>236</v>
+      </c>
+      <c r="E63" t="s">
+        <v>386</v>
+      </c>
+      <c r="F63" t="s">
+        <v>392</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>545</v>
+      </c>
+      <c r="B64" t="s">
+        <v>546</v>
+      </c>
+      <c r="C64" t="s">
+        <v>547</v>
+      </c>
+      <c r="D64" t="s">
+        <v>236</v>
+      </c>
+      <c r="E64" t="s">
+        <v>548</v>
+      </c>
+      <c r="F64" t="s">
+        <v>549</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>551</v>
+      </c>
+      <c r="B65" t="s">
+        <v>552</v>
+      </c>
+      <c r="C65" t="s">
+        <v>553</v>
+      </c>
+      <c r="D65" t="s">
+        <v>236</v>
+      </c>
+      <c r="E65" t="s">
+        <v>386</v>
+      </c>
+      <c r="F65" t="s">
+        <v>554</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>556</v>
+      </c>
+      <c r="B66" t="s">
+        <v>557</v>
+      </c>
+      <c r="C66" t="s">
+        <v>558</v>
+      </c>
+      <c r="D66" t="s">
+        <v>236</v>
+      </c>
+      <c r="E66" t="s">
+        <v>559</v>
+      </c>
+      <c r="F66" t="s">
+        <v>560</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>562</v>
+      </c>
+      <c r="B67" t="s">
+        <v>563</v>
+      </c>
+      <c r="C67" t="s">
+        <v>323</v>
+      </c>
+      <c r="D67" t="s">
+        <v>236</v>
+      </c>
+      <c r="E67" t="s">
+        <v>564</v>
+      </c>
+      <c r="F67" t="s">
+        <v>565</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>567</v>
+      </c>
+      <c r="B68" t="s">
+        <v>568</v>
+      </c>
+      <c r="C68" t="s">
+        <v>569</v>
+      </c>
+      <c r="D68" t="s">
+        <v>236</v>
+      </c>
+      <c r="E68" t="s">
+        <v>570</v>
+      </c>
+      <c r="F68" t="s">
+        <v>436</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>572</v>
+      </c>
+      <c r="B69" t="s">
+        <v>568</v>
+      </c>
+      <c r="C69" t="s">
+        <v>573</v>
+      </c>
+      <c r="D69" t="s">
+        <v>236</v>
+      </c>
+      <c r="E69" t="s">
+        <v>574</v>
+      </c>
+      <c r="F69" t="s">
+        <v>392</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>576</v>
+      </c>
+      <c r="B70" t="s">
+        <v>577</v>
+      </c>
+      <c r="C70" t="s">
+        <v>578</v>
+      </c>
+      <c r="D70" t="s">
+        <v>236</v>
+      </c>
+      <c r="E70" t="s">
+        <v>579</v>
+      </c>
+      <c r="F70" t="s">
+        <v>580</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>582</v>
+      </c>
+      <c r="B71" t="s">
+        <v>583</v>
+      </c>
+      <c r="C71" t="s">
+        <v>534</v>
+      </c>
+      <c r="D71" t="s">
+        <v>236</v>
+      </c>
+      <c r="E71" t="s">
+        <v>584</v>
+      </c>
+      <c r="F71" t="s">
+        <v>585</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>587</v>
+      </c>
+      <c r="B72" t="s">
+        <v>588</v>
+      </c>
+      <c r="C72" t="s">
+        <v>323</v>
+      </c>
+      <c r="D72" t="s">
+        <v>236</v>
+      </c>
+      <c r="E72" t="s">
+        <v>589</v>
+      </c>
+      <c r="F72" t="s">
+        <v>590</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>592</v>
+      </c>
+      <c r="B73" t="s">
+        <v>593</v>
+      </c>
+      <c r="C73" t="s">
+        <v>254</v>
+      </c>
+      <c r="D73" t="s">
+        <v>236</v>
+      </c>
+      <c r="E73" t="s">
+        <v>594</v>
+      </c>
+      <c r="F73" t="s">
+        <v>366</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>596</v>
+      </c>
+      <c r="B74" t="s">
+        <v>597</v>
+      </c>
+      <c r="C74" t="s">
+        <v>254</v>
+      </c>
+      <c r="D74" t="s">
+        <v>598</v>
+      </c>
+      <c r="E74" t="s">
+        <v>599</v>
+      </c>
+      <c r="F74" t="s">
+        <v>600</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>602</v>
+      </c>
+      <c r="B75" t="s">
+        <v>603</v>
+      </c>
+      <c r="C75" t="s">
+        <v>604</v>
+      </c>
+      <c r="D75" t="s">
+        <v>598</v>
+      </c>
+      <c r="E75" t="s">
+        <v>605</v>
+      </c>
+      <c r="F75" t="s">
+        <v>606</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>608</v>
+      </c>
+      <c r="B76" t="s">
+        <v>609</v>
+      </c>
+      <c r="C76" t="s">
+        <v>323</v>
+      </c>
+      <c r="D76" t="s">
+        <v>236</v>
+      </c>
+      <c r="E76" t="s">
+        <v>610</v>
+      </c>
+      <c r="F76" t="s">
+        <v>611</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>613</v>
+      </c>
+      <c r="B77" t="s">
+        <v>614</v>
+      </c>
+      <c r="C77" t="s">
+        <v>254</v>
+      </c>
+      <c r="D77" t="s">
+        <v>236</v>
+      </c>
+      <c r="E77" t="s">
+        <v>615</v>
+      </c>
+      <c r="F77" t="s">
+        <v>386</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>617</v>
+      </c>
+      <c r="B78" t="s">
+        <v>618</v>
+      </c>
+      <c r="C78" t="s">
+        <v>306</v>
+      </c>
+      <c r="D78" t="s">
+        <v>236</v>
+      </c>
+      <c r="E78" t="s">
+        <v>619</v>
+      </c>
+      <c r="F78" t="s">
+        <v>620</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>622</v>
+      </c>
+      <c r="B79" t="s">
+        <v>623</v>
+      </c>
+      <c r="C79" t="s">
+        <v>254</v>
+      </c>
+      <c r="D79" t="s">
+        <v>624</v>
+      </c>
+      <c r="E79" t="s">
+        <v>625</v>
+      </c>
+      <c r="F79" t="s">
+        <v>386</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>627</v>
+      </c>
+      <c r="B80" t="s">
+        <v>628</v>
+      </c>
+      <c r="C80" t="s">
+        <v>629</v>
+      </c>
+      <c r="D80" t="s">
+        <v>236</v>
+      </c>
+      <c r="E80" t="s">
+        <v>630</v>
+      </c>
+      <c r="F80" t="s">
+        <v>631</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>633</v>
+      </c>
+      <c r="B81" t="s">
+        <v>634</v>
+      </c>
+      <c r="C81" t="s">
+        <v>353</v>
+      </c>
+      <c r="D81" t="s">
+        <v>236</v>
+      </c>
+      <c r="E81" t="s">
+        <v>386</v>
+      </c>
+      <c r="F81" t="s">
+        <v>635</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>633</v>
+      </c>
+      <c r="B82" t="s">
+        <v>634</v>
+      </c>
+      <c r="C82" t="s">
+        <v>637</v>
+      </c>
+      <c r="D82" t="s">
+        <v>236</v>
+      </c>
+      <c r="E82" t="s">
+        <v>386</v>
+      </c>
+      <c r="F82" t="s">
+        <v>635</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>639</v>
+      </c>
+      <c r="B83" t="s">
+        <v>640</v>
+      </c>
+      <c r="C83" t="s">
+        <v>641</v>
+      </c>
+      <c r="D83" t="s">
+        <v>236</v>
+      </c>
+      <c r="E83" t="s">
+        <v>642</v>
+      </c>
+      <c r="F83" t="s">
+        <v>386</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>644</v>
+      </c>
+      <c r="B84" t="s">
+        <v>645</v>
+      </c>
+      <c r="C84" t="s">
+        <v>534</v>
+      </c>
+      <c r="D84" t="s">
+        <v>236</v>
+      </c>
+      <c r="E84" t="s">
+        <v>386</v>
+      </c>
+      <c r="F84" t="s">
+        <v>386</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>647</v>
+      </c>
+      <c r="B85" t="s">
+        <v>648</v>
+      </c>
+      <c r="C85" t="s">
+        <v>649</v>
+      </c>
+      <c r="D85" t="s">
+        <v>236</v>
+      </c>
+      <c r="E85" t="s">
+        <v>255</v>
+      </c>
+      <c r="F85" t="s">
+        <v>650</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>652</v>
+      </c>
+      <c r="B86" t="s">
+        <v>653</v>
+      </c>
+      <c r="C86" t="s">
+        <v>235</v>
+      </c>
+      <c r="D86" t="s">
+        <v>236</v>
+      </c>
+      <c r="E86" t="s">
+        <v>654</v>
+      </c>
+      <c r="F86" t="s">
+        <v>655</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>657</v>
+      </c>
+      <c r="B87" t="s">
+        <v>658</v>
+      </c>
+      <c r="C87" t="s">
+        <v>659</v>
+      </c>
+      <c r="D87" t="s">
+        <v>236</v>
+      </c>
+      <c r="E87" t="s">
+        <v>660</v>
+      </c>
+      <c r="F87" t="s">
+        <v>661</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>663</v>
+      </c>
+      <c r="B88" t="s">
+        <v>293</v>
+      </c>
+      <c r="C88" t="s">
+        <v>664</v>
+      </c>
+      <c r="D88" t="s">
+        <v>236</v>
+      </c>
+      <c r="E88" t="s">
+        <v>295</v>
+      </c>
+      <c r="F88" t="s">
+        <v>296</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>666</v>
+      </c>
+      <c r="B89" t="s">
+        <v>667</v>
+      </c>
+      <c r="C89" t="s">
+        <v>254</v>
+      </c>
+      <c r="D89" t="s">
+        <v>236</v>
+      </c>
+      <c r="E89" t="s">
+        <v>668</v>
+      </c>
+      <c r="F89" t="s">
+        <v>669</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>671</v>
+      </c>
+      <c r="B90" t="s">
+        <v>672</v>
+      </c>
+      <c r="C90" t="s">
+        <v>673</v>
+      </c>
+      <c r="D90" t="s">
+        <v>236</v>
+      </c>
+      <c r="E90" t="s">
+        <v>674</v>
+      </c>
+      <c r="F90" t="s">
+        <v>284</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>676</v>
+      </c>
+      <c r="B91" t="s">
+        <v>677</v>
+      </c>
+      <c r="C91" t="s">
+        <v>254</v>
+      </c>
+      <c r="D91" t="s">
+        <v>236</v>
+      </c>
+      <c r="E91" t="s">
+        <v>678</v>
+      </c>
+      <c r="F91" t="s">
+        <v>679</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>681</v>
+      </c>
+      <c r="B92" t="s">
+        <v>677</v>
+      </c>
+      <c r="C92" t="s">
+        <v>254</v>
+      </c>
+      <c r="D92" t="s">
+        <v>236</v>
+      </c>
+      <c r="E92" t="s">
+        <v>678</v>
+      </c>
+      <c r="F92" t="s">
+        <v>682</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>684</v>
+      </c>
+      <c r="B93" t="s">
+        <v>685</v>
+      </c>
+      <c r="C93" t="s">
+        <v>254</v>
+      </c>
+      <c r="D93" t="s">
+        <v>236</v>
+      </c>
+      <c r="E93" t="s">
+        <v>386</v>
+      </c>
+      <c r="F93" t="s">
+        <v>366</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>687</v>
+      </c>
+      <c r="B94" t="s">
+        <v>688</v>
+      </c>
+      <c r="C94" t="s">
+        <v>689</v>
+      </c>
+      <c r="D94" t="s">
+        <v>335</v>
+      </c>
+      <c r="E94" t="s">
+        <v>386</v>
+      </c>
+      <c r="F94" t="s">
+        <v>690</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>692</v>
+      </c>
+      <c r="B95" t="s">
+        <v>693</v>
+      </c>
+      <c r="C95" t="s">
+        <v>477</v>
+      </c>
+      <c r="D95" t="s">
+        <v>236</v>
+      </c>
+      <c r="E95" t="s">
+        <v>694</v>
+      </c>
+      <c r="F95" t="s">
+        <v>695</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>697</v>
+      </c>
+      <c r="B96" t="s">
+        <v>698</v>
+      </c>
+      <c r="C96" t="s">
+        <v>254</v>
+      </c>
+      <c r="D96" t="s">
+        <v>347</v>
+      </c>
+      <c r="E96" t="s">
+        <v>699</v>
+      </c>
+      <c r="F96" t="s">
+        <v>700</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>702</v>
+      </c>
+      <c r="B97" t="s">
+        <v>563</v>
+      </c>
+      <c r="C97" t="s">
+        <v>703</v>
+      </c>
+      <c r="D97" t="s">
+        <v>236</v>
+      </c>
+      <c r="E97" t="s">
+        <v>704</v>
+      </c>
+      <c r="F97" t="s">
+        <v>565</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>706</v>
+      </c>
+      <c r="B98" t="s">
+        <v>460</v>
+      </c>
+      <c r="C98" t="s">
+        <v>707</v>
+      </c>
+      <c r="D98" t="s">
+        <v>236</v>
+      </c>
+      <c r="E98" t="s">
+        <v>462</v>
+      </c>
+      <c r="F98" t="s">
+        <v>708</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>710</v>
+      </c>
+      <c r="B99" t="s">
+        <v>711</v>
+      </c>
+      <c r="C99" t="s">
+        <v>430</v>
+      </c>
+      <c r="D99" t="s">
+        <v>236</v>
+      </c>
+      <c r="E99" t="s">
+        <v>712</v>
+      </c>
+      <c r="F99" t="s">
+        <v>713</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>715</v>
+      </c>
+      <c r="B100" t="s">
+        <v>716</v>
+      </c>
+      <c r="C100" t="s">
+        <v>717</v>
+      </c>
+      <c r="D100" t="s">
+        <v>347</v>
+      </c>
+      <c r="E100" t="s">
+        <v>718</v>
+      </c>
+      <c r="F100" t="s">
+        <v>719</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>715</v>
+      </c>
+      <c r="B101" t="s">
+        <v>721</v>
+      </c>
+      <c r="C101" t="s">
+        <v>722</v>
+      </c>
+      <c r="D101" t="s">
+        <v>236</v>
+      </c>
+      <c r="E101" t="s">
+        <v>723</v>
+      </c>
+      <c r="F101" t="s">
+        <v>724</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>726</v>
+      </c>
+      <c r="B102" t="s">
+        <v>716</v>
+      </c>
+      <c r="C102" t="s">
+        <v>717</v>
+      </c>
+      <c r="D102" t="s">
+        <v>347</v>
+      </c>
+      <c r="E102" t="s">
+        <v>718</v>
+      </c>
+      <c r="F102" t="s">
+        <v>719</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>728</v>
+      </c>
+      <c r="B103" t="s">
+        <v>716</v>
+      </c>
+      <c r="C103" t="s">
+        <v>717</v>
+      </c>
+      <c r="D103" t="s">
+        <v>347</v>
+      </c>
+      <c r="E103" t="s">
+        <v>718</v>
+      </c>
+      <c r="F103" t="s">
+        <v>719</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>729</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-10-08.xlsx
+++ b/docs/xlsx/jobs-2026-10-08.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="730">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1462" uniqueCount="914">
   <si>
     <t>Title</t>
   </si>
@@ -715,6 +715,24 @@
     <t>https://greenjobs.greenjobsearch.org/jobs/energy-assessor-1/</t>
   </si>
   <si>
+    <t>Regional Campaign Manager, Northern California</t>
+  </si>
+  <si>
+    <t>Greenlight America</t>
+  </si>
+  <si>
+    <t>California, United States, United States</t>
+  </si>
+  <si>
+    <t>Clean Energy</t>
+  </si>
+  <si>
+    <t>Idealist</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/regional-campaign-manager-northern-california/</t>
+  </si>
+  <si>
     <t>Advocate (bilingual in English and Spanish)</t>
   </si>
   <si>
@@ -736,6 +754,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/2b12970c8fc14cb1acc5890ffece59bc-advocate-bilingual-in-english-and-spanish-the-networkla-red-boston</t>
   </si>
   <si>
+    <t>Alhadeff Studio Head Technician</t>
+  </si>
+  <si>
+    <t>Seattle Repertory Theatre</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>USD 34.00 - 34.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c4e41c72cb5a40a893ab850f41e38527-alhadeff-studio-head-technician-seattle-repertory-theatre-seattle</t>
+  </si>
+  <si>
     <t>Analista de Alianzas y Estrategias para Fundraising</t>
   </si>
   <si>
@@ -790,6 +826,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/4f707a1fea57403b94c44726984de059-assistant-program-director-camp-naru-ys-kim-foundation-new-york</t>
   </si>
   <si>
+    <t>Assistant to Director</t>
+  </si>
+  <si>
+    <t>The Posse Foundation, Bay Area</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 44000.00/year</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7b479c154e424cec9614e4b63e8d72cb-assistant-to-director-the-posse-foundation-bay-area-san-francisco</t>
+  </si>
+  <si>
     <t>Assistente de Recrutamento e Acolhimento</t>
   </si>
   <si>
@@ -850,9 +904,6 @@
     <t>Katonah, New York</t>
   </si>
   <si>
-    <t>Arts Music</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/5ebbf3e4867a41e1817d390003ca5ae8-associate-director-of-development-katonah-museum-of-art-katonah</t>
   </si>
   <si>
@@ -910,6 +961,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/7035a80efb4440ccabfeedf52e488df3-bilingual-client-services-coordinator-community-servings-inc-jamaica</t>
   </si>
   <si>
+    <t>Biologist - Work with rescued wildlife in the Bolivian Amazon</t>
+  </si>
+  <si>
+    <t>Comunidad Inti Wara Yassi (CIWY)</t>
+  </si>
+  <si>
+    <t>Ascensión de Guarayos, Santa Cruz, BO</t>
+  </si>
+  <si>
+    <t>BOB 2000.00/month</t>
+  </si>
+  <si>
+    <t>Animals, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/07f9c9515db94e349ca2846ab604546c-biologist-work-with-rescued-wildlife-in-the-bolivian-amazon-comunidad-inti-wara-yassi-ciwy-ascension-de-guarayos</t>
+  </si>
+  <si>
     <t>Building Green Futures Lead Trainer</t>
   </si>
   <si>
@@ -946,6 +1015,141 @@
     <t>https://www.idealist.org/en/nonprofit-job/8643de3ce380451aa736f449a4441cb0-business-development-officer-equimundo-washington</t>
   </si>
   <si>
+    <t>California Conservation Campaign Associate</t>
+  </si>
+  <si>
+    <t>Environment America</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 40000.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dbf807b9b1e5481591464cb20c2209c8-california-conservation-campaign-associate-environment-america-oakland</t>
+  </si>
+  <si>
+    <t>Campaign Associate for Non-profit</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 44450.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c0948631bef147179cb104cbebbc374a-campaign-associate-for-non-profit-environment-america-washington</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/29a069a9348d4ebd900548f201aa045b-campaign-associate-for-non-profit-environment-america-portland</t>
+  </si>
+  <si>
+    <t>Ann Arbor, Michigan</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/189d8269eff74d2a855eb66bb67de23a-campaign-associate-for-non-profit-environment-america-ann-arbor</t>
+  </si>
+  <si>
+    <t>Campus Organizer</t>
+  </si>
+  <si>
+    <t>Student PIRGs</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Consumer Protection, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ff32032407a94045a0261eb2fee03aff-campus-organizer-student-pirgs-philadelphia</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d19af6abf5b44cacbce41b64a16ddbdc-campus-organizer-student-pirgs-boston</t>
+  </si>
+  <si>
+    <t>New Brunswick, New Jersey</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c82fad0953ef498e8a35638ce1e011f3-campus-organizer-student-pirgs-new-brunswick</t>
+  </si>
+  <si>
+    <t>Eugene, Oregon</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a7aa05f420b84e77bb036a3c892e13fe-campus-organizer-student-pirgs-eugene</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a6713f24e3ef4348ac34983a6d6dd0a6-campus-organizer-student-pirgs-chicago</t>
+  </si>
+  <si>
+    <t>Madison, Wisconsin</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a585e9fc66314dbda56d07b80af83580-campus-organizer-student-pirgs-madison</t>
+  </si>
+  <si>
+    <t>Amherst, Massachusetts</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/87e0f653c59e48d08f6ee8b2492f1162-campus-organizer-student-pirgs-amherst</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5f3bbd6ab6af4d73b31fed36f71ff7ac-campus-organizer-student-pirgs-los-angeles</t>
+  </si>
+  <si>
+    <t>San Diego, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/58b33ec21d854d59a23e0bf289844932-campus-organizer-student-pirgs-san-diego</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/515c3440cd274a6e89908f45e6c01d72-campus-organizer-student-pirgs-ann-arbor</t>
+  </si>
+  <si>
+    <t>Minneapolis, Minnesota</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/34f4a3c0fd444334b78befad7cd1b23e-campus-organizer-student-pirgs-minneapolis</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2b8e4b2fa38549dc9cbbfc772d7c3c18-campus-organizer-student-pirgs-seattle</t>
+  </si>
+  <si>
+    <t>Raleigh, North Carolina</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0db08ab09e994100b745f07fece081ee-campus-organizer-student-pirgs-raleigh</t>
+  </si>
+  <si>
+    <t>Berkeley, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0429baf7e04b4636b08a9c9eaf694746-campus-organizer-student-pirgs-berkeley</t>
+  </si>
+  <si>
+    <t>Career Program Specialists</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 57000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4b3c60e58db44cb990085746c6df6abc-career-program-specialists-the-posse-foundation-bay-area-san-francisco</t>
+  </si>
+  <si>
     <t>Chapter Organizer</t>
   </si>
   <si>
@@ -1033,6 +1237,12 @@
     <t>https://www.idealist.org/en/nonprofit-job/980f75b8af7045f99479bef8da96fccd-civic-engagement-organizer-iowa-united-today-stronger-tomorrow-salt-lake-city</t>
   </si>
   <si>
+    <t>Clean Water Campaign Associate</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9baa2b41d29b4cf99d7c87b8f8fa9d7b-clean-water-campaign-associate-environment-america-philadelphia</t>
+  </si>
+  <si>
     <t>Community Engagement Associate - Spanish</t>
   </si>
   <si>
@@ -1051,6 +1261,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/4f42c0f2f158411396ea93d398abb9a0-community-engagement-associate-spanish-nyc-kids-rise-long-island-city</t>
   </si>
   <si>
+    <t>Community Manager @ Fcancer!</t>
+  </si>
+  <si>
+    <t>Fuck Cancer</t>
+  </si>
+  <si>
+    <t>USD 3000.00 - 5000.00/month</t>
+  </si>
+  <si>
+    <t>Entrepreneurship, Health Medicine, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f55d20951d6f4bcead4d3cfcd01d01fa-community-manager-fcancer-fuck-cancer-los-angeles</t>
+  </si>
+  <si>
     <t>Community Reentry Program Lead</t>
   </si>
   <si>
@@ -1069,6 +1294,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/1445f459900740018e1f56cdc786f26d-community-reentry-program-lead-the-phoenix-boston</t>
   </si>
   <si>
+    <t>Conservation Advocate - Oceans</t>
+  </si>
+  <si>
+    <t>USD 41750.00 - 46000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/40494005d1c24c129c4c9bfc5521f031-conservation-advocate-oceans-environment-america-boston</t>
+  </si>
+  <si>
     <t>Consultoría en psiquiatría</t>
   </si>
   <si>
@@ -1087,6 +1321,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/a7f8a590112f4ff1b5b4fb047dc5efa2-consultoria-en-psiquiatria-companeros-en-salud-angel-albino-corzo</t>
   </si>
   <si>
+    <t>Consumer Advocacy Campaign Associate</t>
+  </si>
+  <si>
+    <t>U.S. PIRG</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Transparency Oversight, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/65c56a842b004fb19db687673bcfaaa2-consumer-advocacy-campaign-associate-us-pirg-los-angeles</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4c15c2185ed944f085a146bc10adac8b-consumer-advocacy-campaign-associate-us-pirg-boston</t>
+  </si>
+  <si>
     <t>Development Coordinator</t>
   </si>
   <si>
@@ -1105,6 +1354,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/e977a4ef2c924064b2be2e81510b4d03-development-coordinator-two-ten-footwear-foundation-waltham</t>
   </si>
   <si>
+    <t>Latinas On the Verge of Excellence - LOVE, Inc</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Education, Children Youth, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dc1eaaa496634403832d99e5b5261a99-development-coordinator-latinas-on-the-verge-of-excellence-love-inc-new-york</t>
+  </si>
+  <si>
     <t>Development Manager</t>
   </si>
   <si>
@@ -1141,9 +1405,6 @@
     <t>PARKINSON &amp; MOVEMENT DISORDER ALLIANCE</t>
   </si>
   <si>
-    <t>USD 55000.00 - 57000.00/year</t>
-  </si>
-  <si>
     <t>Health Medicine, Seniors Retirement</t>
   </si>
   <si>
@@ -1174,9 +1435,6 @@
     <t>USD 100000.00 - 120000.00/year</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/1647407592204ba8887d20aadc2865d4-director-of-administration-and-finance-weeksville-heritage-center-kings-county</t>
   </si>
   <si>
@@ -1219,6 +1477,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/d0ebc90255f744359a366ebde90d48ec-director-of-internal-operations-at-nechama-jewish-response-to-disaster-nechama-jewish-response-to-disaster-saint-paul</t>
   </si>
   <si>
+    <t>Director of Program Implementation</t>
+  </si>
+  <si>
+    <t>Summer Search</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>USD 112705.00 - 121295.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dfc7c3631bba488ba305138047e8a868-director-of-program-implementation-summer-search-oakland</t>
+  </si>
+  <si>
     <t>Donor Engagement Specialist, Travel</t>
   </si>
   <si>
@@ -1261,6 +1537,75 @@
     <t>https://www.idealist.org/en/nonprofit-job/75120d564e604797825e3f2872fd7ce8-ell-instructor-at-rikers-island-full-time-or-part-time-the-petey-greene-program-new-york</t>
   </si>
   <si>
+    <t>End Food Waste Advocate</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4840d4cca25046999c0ebd47f37cad8e-end-food-waste-advocate-us-pirg-chicago</t>
+  </si>
+  <si>
+    <t>Environmental Campaign Organizer</t>
+  </si>
+  <si>
+    <t>Green Corps</t>
+  </si>
+  <si>
+    <t>Denver, Colorado</t>
+  </si>
+  <si>
+    <t>USD 41000.00 - 44450.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fa63e70f8d3b422a937101d6fe0e05e7-environmental-campaign-organizer-green-corps-denver</t>
+  </si>
+  <si>
+    <t>Columbus, Ohio</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d606a5c4556d4e31951d5906d1a2f984-environmental-campaign-organizer-green-corps-columbus</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/898e5fa012964518a9aa99b273c25a36-environmental-campaign-organizer-green-corps-portland</t>
+  </si>
+  <si>
+    <t>Austin, Texas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7b835837c0c844aeba04945400b7ddb7-environmental-campaign-organizer-green-corps-austin</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/613dfeacec5d430f870eba569daa9a1f-environmental-campaign-organizer-green-corps-washington</t>
+  </si>
+  <si>
+    <t>St. Louis, Missouri</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3ae2f182c94547e6ba917b654b22a521-environmental-campaign-organizer-green-corps-st-louis</t>
+  </si>
+  <si>
+    <t>Nashville, Tennessee</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/376d8d7536f148d0b07398006e558a42-environmental-campaign-organizer-green-corps-nashville</t>
+  </si>
+  <si>
+    <t>Charlotte, North Carolina</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1191680b24704c278f8b332d1a00045e-environmental-campaign-organizer-green-corps-charlotte</t>
+  </si>
+  <si>
+    <t>Orlando, Florida</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/88e731b71788436a91b83062b0d1b8ba-environmental-campaign-organizer-green-corps-orlando</t>
+  </si>
+  <si>
+    <t>Detroit, Michigan</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6a6886a047ce42138a6c7ed0ec59e91c-environmental-campaign-organizer-green-corps-detroit</t>
+  </si>
+  <si>
     <t>Event Coordinator</t>
   </si>
   <si>
@@ -1306,12 +1651,21 @@
     <t>Multnomah Athletic Foundation</t>
   </si>
   <si>
-    <t>Portland, Oregon</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/job/e34d65209bf54e8e9c0cdc87f3372286-executive-director-multnomah-athletic-foundation-portland</t>
   </si>
   <si>
+    <t>Executive Director: Green Lake School Age Child Care Program</t>
+  </si>
+  <si>
+    <t>Green Lake School Age Care Program (GLSA)</t>
+  </si>
+  <si>
+    <t>USD 82400.00 - 87000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3502454763834518a246aaf2b9d4bfbf-executive-director-green-lake-school-age-child-care-program-green-lake-school-age-care-program-glsa-seattle</t>
+  </si>
+  <si>
     <t>Facilitador/a Educativo/a en Michoacán ( Morelia o Capula )</t>
   </si>
   <si>
@@ -1396,9 +1750,6 @@
     <t>Head Veterinarian - Work in the Bolivian Jungle with rescued wildlife</t>
   </si>
   <si>
-    <t>Comunidad Inti Wara Yassi (CIWY)</t>
-  </si>
-  <si>
     <t>San Buenaventura, La Paz, BO</t>
   </si>
   <si>
@@ -1435,9 +1786,6 @@
     <t>USD 65000.00 - 75000.00/year</t>
   </si>
   <si>
-    <t>Children Youth, Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/da859246f59a4dd382251ab8c799c3a0-high-school-sat-teacher-success-academy-charter-schools-new-york</t>
   </si>
   <si>
@@ -1525,9 +1873,6 @@
     <t>Seva Foundation</t>
   </si>
   <si>
-    <t>Berkeley, California</t>
-  </si>
-  <si>
     <t>Community Development, Economic Development, Health Medicine</t>
   </si>
   <si>
@@ -1570,6 +1915,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/40f9387a47ff43a28ab791645f4f600e-justice-in-public-safety-project-counsel-naacp-legal-defense-and-educational-fund-inc-new-york</t>
   </si>
   <si>
+    <t>Lactation Care Coordinator (IBCLC)</t>
+  </si>
+  <si>
+    <t>Mamatoto Village</t>
+  </si>
+  <si>
+    <t>USD 76000.00 - 82000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Reproductive Health Rights, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cd84abb17e9b490c8fc0aa035bc7a068-lactation-care-coordinator-ibclc-mamatoto-village-washington</t>
+  </si>
+  <si>
+    <t>Lead Program Facilitator</t>
+  </si>
+  <si>
+    <t>exalt youth</t>
+  </si>
+  <si>
+    <t>Syracuse, New York</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ff41b161ffb64a2987ae822a4825638f-lead-program-facilitator-exalt-youth-syracuse</t>
+  </si>
+  <si>
     <t>Learning Content Manager, SAGECare</t>
   </si>
   <si>
@@ -1618,9 +1993,6 @@
     <t>Loevy + Loevy</t>
   </si>
   <si>
-    <t>Chicago, Illinois</t>
-  </si>
-  <si>
     <t>Human Rights Civil Liberties, Transparency Oversight, Legal Assistance</t>
   </si>
   <si>
@@ -1645,9 +2017,6 @@
     <t>Wissahickon Charter School</t>
   </si>
   <si>
-    <t>Philadelphia, Pennsylvania</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/9282ec97922a4394bb9b36010ca7bfd8-middle-school-math-teachers-wissahickon-charter-school-philadelphia</t>
   </si>
   <si>
@@ -1717,6 +2086,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/cf9b5ecd5a4a4e45aa4e6adebc256373-network-development-national-initiatives-director-council-on-american-islamic-relations-national-headquarters-washington</t>
   </si>
   <si>
+    <t>Nonprofit Consumer Advocate</t>
+  </si>
+  <si>
+    <t>USD 41750.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Transparency Oversight</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a1f82e18374e4b90a3d4c3b0cac90f26-nonprofit-consumer-advocate-us-pirg-austin</t>
+  </si>
+  <si>
+    <t>North Carolina Conservation Advocate</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ed609520da99401bb36cce09bdab2f7d-north-carolina-conservation-advocate-environment-america-raleigh</t>
+  </si>
+  <si>
     <t>NY Middle School Math Teacher SY26-27</t>
   </si>
   <si>
@@ -1744,6 +2131,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/0b9e9fdabef14b0aaf33aa28cad02606-ny-middle-school-science-teacher-sy26-27-excellence-community-schools-bronx</t>
   </si>
   <si>
+    <t>Oakland Goes OutDoor - Fractional Executive Director</t>
+  </si>
+  <si>
+    <t>Oakland Public Education Fund</t>
+  </si>
+  <si>
+    <t>USD 97500.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ce17cd5b4edb445ca8b53a82fbea2fa2-oakland-goes-outdoor-fractional-executive-director-oakland-public-education-fund-oakland</t>
+  </si>
+  <si>
     <t>Office Coordinator (Secretariat Office)</t>
   </si>
   <si>
@@ -1777,6 +2179,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/496acc0438a643a9b7e1f75937ca8b85-operations-administrative-assistant-paul-angell-foundation-chicago</t>
   </si>
   <si>
+    <t>Operations Associate</t>
+  </si>
+  <si>
+    <t>California ChangeLawyers</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 54000.00 - 54000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a35ff51703cf49ed8c12d5faadf9efb2-operations-associate-california-changelawyers-san-francisco</t>
+  </si>
+  <si>
     <t>Operations, HR &amp; Development Manager</t>
   </si>
   <si>
@@ -1804,15 +2224,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/3885f5cc661a40aeb93104aba0b7039e-paralegal-client-advocate-prison-based-services-appellate-advocates-new-york</t>
   </si>
   <si>
+    <t>Paralegal Case Manager</t>
+  </si>
+  <si>
+    <t>Housing Rights Center</t>
+  </si>
+  <si>
+    <t>Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>USD 58000.00 - 63000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1480f4031bcb4640b882e91629a98c00-paralegal-case-manager-housing-rights-center-los-angeles</t>
+  </si>
+  <si>
     <t>Part-time Math Instructional Coach serving Entering and Emerging Multilingual Learners - 19 hours weekly (2.5 days)</t>
   </si>
   <si>
     <t>Bridges to Academic Success</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>USD 40.00 - 50.00/hour</t>
   </si>
   <si>
@@ -1867,6 +2302,12 @@
     <t>https://www.idealist.org/en/business-job/9071ec029b7747bf8642c5c28fece046-product-portfolio-director-full-time-position-hybrid-cause-strategy-partners-new-york</t>
   </si>
   <si>
+    <t>Profesional en Biología - Trabaja con Fauna Silvestre Rescatada en la Selva Boliviana</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f16da72b8f4e4be2bf53f0954639a926-profesional-en-biologia-trabaja-con-fauna-silvestre-rescatada-en-la-selva-boliviana-comunidad-inti-wara-yassi-ciwy-ascension-de-guarayos</t>
+  </si>
+  <si>
     <t>Program Assistant - Conservation</t>
   </si>
   <si>
@@ -1882,54 +2323,78 @@
     <t>https://www.idealist.org/en/nonprofit-job/d38d820622ba4374bc7f96dc6099eb3f-program-assistant-conservation-the-wyss-foundation-washington</t>
   </si>
   <si>
+    <t>Program Coordinator “See It and Be It” (Richmond Area) - Part time / Temporary</t>
+  </si>
+  <si>
+    <t>STEAM the Streets</t>
+  </si>
+  <si>
+    <t>Richmond, California</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ceb3c9e8064a459d98181170a6c12ebd-program-coordinator-see-it-and-be-it-richmond-area-part-time-temporary-steam-the-streets-richmond</t>
+  </si>
+  <si>
+    <t>Program Director</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/53813e3fe6be4ee59e3cc1c7c50cb6ef-program-director-the-posse-foundation-bay-area-san-francisco</t>
+  </si>
+  <si>
     <t>Recruiter (Part-time, Temporary)</t>
   </si>
   <si>
     <t>Columbia University, Office of Alumni Relations and Development</t>
   </si>
   <si>
-    <t>Part Time, Temporary</t>
-  </si>
-  <si>
-    <t>USD 40000.00 - 40000.00/year</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/358211387aae4d3287d2e39aa0f085f1-recruiter-part-time-temporary-columbia-university-office-of-alumni-relations-and-development-new-york</t>
   </si>
   <si>
-    <t>Regional Campaign Manager, Northern California</t>
-  </si>
-  <si>
-    <t>Greenlight America</t>
-  </si>
-  <si>
-    <t>Remote (California)</t>
-  </si>
-  <si>
     <t>USD 75000.00 - 100000.00/year</t>
   </si>
   <si>
     <t>Climate Change, Energy</t>
   </si>
   <si>
+    <t>Green Jobs</t>
+  </si>
+  <si>
     <t>https://www.idealist.org/en/nonprofit-job/9a4cd646906b45ddad4bf16e933e8997-regional-campaign-manager-northern-california-greenlight-america-washington</t>
   </si>
   <si>
+    <t>Sales &amp; Partnerships Associate</t>
+  </si>
+  <si>
+    <t>Mercado Global</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fe50a40fd8bd413aafc608e3ad606de2-sales-partnerships-associate-mercado-global-brooklyn</t>
+  </si>
+  <si>
+    <t>Remote (GT)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c258d13c70f54c308f2e05ac606be756-sales-partnerships-associate-mercado-global-brooklyn</t>
+  </si>
+  <si>
     <t>Sales Associate</t>
   </si>
   <si>
-    <t>Mercado Global</t>
-  </si>
-  <si>
-    <t>Community Development, Education, Women</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/fe50a40fd8bd413aafc608e3ad606de2-sales-associate-mercado-global-brooklyn</t>
   </si>
   <si>
-    <t>Remote (GT)</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/c258d13c70f54c308f2e05ac606be756-sales-associate-mercado-global-brooklyn</t>
   </si>
   <si>
@@ -1957,6 +2422,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/05f20beba07f4eee8f6ab837f33c0713-senior-attorney-or-counsel-lambda-legal-chicago</t>
   </si>
   <si>
+    <t>Senior Brand Reputation &amp; Communications Manager</t>
+  </si>
+  <si>
+    <t>B Lab</t>
+  </si>
+  <si>
+    <t>Amsterdam, North Holland, NL</t>
+  </si>
+  <si>
+    <t>EUR 71000.00 - 71000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Economic Development, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1e60926f5ede4da58e0f1476d7c770fe-senior-brand-reputation-communications-manager-b-lab-amsterdam</t>
+  </si>
+  <si>
     <t>Senior Communications Associate</t>
   </si>
   <si>
@@ -1987,6 +2470,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/7b53023ab0fe40358253f7af54a81a98-senior-director-of-development-empath-boston</t>
   </si>
   <si>
+    <t>Senior HR Generalist</t>
+  </si>
+  <si>
+    <t>Crisis Connections</t>
+  </si>
+  <si>
+    <t>USD 74000.00 - 92000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Mental Health, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/be42764749664f158637d522442b204e-senior-hr-generalist-crisis-connections-seattle</t>
+  </si>
+  <si>
     <t>Senior Immigrant Rights Attorney</t>
   </si>
   <si>
@@ -2005,6 +2503,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/f1068fd9978c4d1ea248a428c7a8aead-senior-immigrant-rights-attorney-legal-aid-justice-center-norfolk</t>
   </si>
   <si>
+    <t>Senior Staff Attorney, Litigation Team</t>
+  </si>
+  <si>
+    <t>The Transgender Law Center</t>
+  </si>
+  <si>
+    <t>USD 118400.00 - 118400.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2a9abae1d2734609aa71416f58ec654b-senior-staff-attorney-litigation-team-the-transgender-law-center-oakland</t>
+  </si>
+  <si>
     <t>Shipper / Receiver</t>
   </si>
   <si>
@@ -2068,6 +2581,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/037860e50b5f4555906456ef187c051e-staff-attorney-mels-matrimonial-unit-district-council-37-health-security-plan-new-york</t>
   </si>
   <si>
+    <t>Staff Attorney, Litigation Team</t>
+  </si>
+  <si>
+    <t>USD 107500.00 - 107500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/144bd04069a044bfb12a8fec67d9b91d-staff-attorney-litigation-team-the-transgender-law-center-oakland</t>
+  </si>
+  <si>
     <t>Staff Attorney, New York Family Unity Project (NYIFUP)</t>
   </si>
   <si>
@@ -2182,9 +2704,6 @@
     <t>The Mountaineers</t>
   </si>
   <si>
-    <t>Seattle, WA</t>
-  </si>
-  <si>
     <t>USD 22.14 - 24.04/hour</t>
   </si>
   <si>
@@ -2192,6 +2711,39 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/3d9b0610744a4c1b874b8ee24332f283-volunteer-coordinator-the-mountaineers-seattle</t>
+  </si>
+  <si>
+    <t>Volunteer Manager</t>
+  </si>
+  <si>
+    <t>Alchemist CDC</t>
+  </si>
+  <si>
+    <t>Sacramento, California</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 30.81/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d4fd7cda0179474fa155b8e6dee8da89-volunteer-manager-alchemist-cdc-sacramento</t>
+  </si>
+  <si>
+    <t>Wish Coordinator</t>
+  </si>
+  <si>
+    <t>Make-A-Wish Alaska &amp; Washington</t>
+  </si>
+  <si>
+    <t>USD 24.00 - 27.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/28ee2f4812cb427c884500131030900d-wish-coordinator-make-a-wish-alaska-washington-seattle</t>
   </si>
   <si>
     <t>Youth Engagement Coordinator</t>
@@ -3599,7 +4151,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3684,11 +4236,38 @@
         <v>232</v>
       </c>
     </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>233</v>
+      </c>
+      <c r="B4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C4" t="s">
+        <v>235</v>
+      </c>
+      <c r="D4" t="s">
+        <v>223</v>
+      </c>
+      <c r="E4" t="s">
+        <v>224</v>
+      </c>
+      <c r="F4" t="s">
+        <v>236</v>
+      </c>
+      <c r="G4" t="s">
+        <v>237</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3697,7 +4276,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H103"/>
+  <dimension ref="A1:H162"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3738,416 +4317,416 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B2" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="C2" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="D2" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E2" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="F2" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B3" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="C3" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="D3" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E3" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="F3" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B4" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C4" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="D4" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E4" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="F4" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B5" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="C5" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E5" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="F5" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B6" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C6" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D6" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E6" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="F6" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B7" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="C7" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="D7" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E7" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="F7" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="B8" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="C8" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="D8" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E8" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="F8" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="B9" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="C9" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="D9" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E9" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="F9" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="B10" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="C10" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="D10" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E10" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="F10" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="B11" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="C11" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="D11" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E11" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="F11" t="s">
-        <v>290</v>
+        <v>250</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B12" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C12" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="D12" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E12" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="F12" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B13" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C13" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="D13" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E13" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="F13" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B14" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C14" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="D14" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E14" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F14" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B15" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C15" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="D15" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E15" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="F15" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B16" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C16" t="s">
-        <v>282</v>
+        <v>323</v>
       </c>
       <c r="D16" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E16" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="F16" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B17" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="C17" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="D17" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E17" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="F17" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B18" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="C18" t="s">
-        <v>254</v>
+        <v>335</v>
       </c>
       <c r="D18" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E18" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="F18" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="B19" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C19" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="D19" t="s">
-        <v>335</v>
+        <v>242</v>
       </c>
       <c r="E19" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F19" t="s">
         <v>337</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -4155,1931 +4734,3291 @@
         <v>339</v>
       </c>
       <c r="B20" t="s">
+        <v>334</v>
+      </c>
+      <c r="C20" t="s">
+        <v>342</v>
+      </c>
+      <c r="D20" t="s">
+        <v>242</v>
+      </c>
+      <c r="E20" t="s">
         <v>340</v>
       </c>
-      <c r="C20" t="s">
-        <v>341</v>
-      </c>
-      <c r="D20" t="s">
-        <v>236</v>
-      </c>
-      <c r="E20" t="s">
-        <v>342</v>
-      </c>
       <c r="F20" t="s">
+        <v>337</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>343</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>339</v>
+      </c>
+      <c r="B21" t="s">
+        <v>334</v>
+      </c>
+      <c r="C21" t="s">
+        <v>344</v>
+      </c>
+      <c r="D21" t="s">
+        <v>242</v>
+      </c>
+      <c r="E21" t="s">
+        <v>340</v>
+      </c>
+      <c r="F21" t="s">
+        <v>337</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>345</v>
-      </c>
-      <c r="B21" t="s">
-        <v>346</v>
-      </c>
-      <c r="C21" t="s">
-        <v>235</v>
-      </c>
-      <c r="D21" t="s">
-        <v>347</v>
-      </c>
-      <c r="E21" t="s">
-        <v>348</v>
-      </c>
-      <c r="F21" t="s">
-        <v>349</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="B22" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="C22" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="D22" t="s">
-        <v>347</v>
+        <v>242</v>
       </c>
       <c r="E22" t="s">
-        <v>354</v>
+        <v>340</v>
       </c>
       <c r="F22" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="B23" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="C23" t="s">
-        <v>359</v>
+        <v>241</v>
       </c>
       <c r="D23" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E23" t="s">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="F23" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="B24" t="s">
-        <v>364</v>
+        <v>347</v>
       </c>
       <c r="C24" t="s">
-        <v>306</v>
+        <v>352</v>
       </c>
       <c r="D24" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E24" t="s">
-        <v>365</v>
+        <v>340</v>
       </c>
       <c r="F24" t="s">
-        <v>366</v>
+        <v>349</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>367</v>
+        <v>353</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>368</v>
+        <v>346</v>
       </c>
       <c r="B25" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
       <c r="C25" t="s">
-        <v>235</v>
+        <v>354</v>
       </c>
       <c r="D25" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E25" t="s">
-        <v>370</v>
+        <v>340</v>
       </c>
       <c r="F25" t="s">
-        <v>371</v>
+        <v>349</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>373</v>
+        <v>346</v>
       </c>
       <c r="B26" t="s">
-        <v>374</v>
+        <v>347</v>
       </c>
       <c r="C26" t="s">
-        <v>323</v>
+        <v>356</v>
       </c>
       <c r="D26" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E26" t="s">
-        <v>375</v>
+        <v>340</v>
       </c>
       <c r="F26" t="s">
-        <v>376</v>
+        <v>349</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>377</v>
+        <v>357</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>378</v>
+        <v>346</v>
       </c>
       <c r="B27" t="s">
-        <v>379</v>
+        <v>347</v>
       </c>
       <c r="C27" t="s">
-        <v>254</v>
+        <v>358</v>
       </c>
       <c r="D27" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E27" t="s">
-        <v>380</v>
+        <v>340</v>
       </c>
       <c r="F27" t="s">
-        <v>278</v>
+        <v>349</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>381</v>
+        <v>359</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>382</v>
+        <v>346</v>
       </c>
       <c r="B28" t="s">
-        <v>383</v>
+        <v>347</v>
       </c>
       <c r="C28" t="s">
-        <v>384</v>
+        <v>360</v>
       </c>
       <c r="D28" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E28" t="s">
-        <v>385</v>
+        <v>340</v>
       </c>
       <c r="F28" t="s">
-        <v>386</v>
+        <v>349</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>387</v>
+        <v>361</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>388</v>
+        <v>346</v>
       </c>
       <c r="B29" t="s">
-        <v>389</v>
+        <v>347</v>
       </c>
       <c r="C29" t="s">
-        <v>390</v>
+        <v>289</v>
       </c>
       <c r="D29" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E29" t="s">
-        <v>391</v>
+        <v>340</v>
       </c>
       <c r="F29" t="s">
-        <v>392</v>
+        <v>349</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>393</v>
+        <v>362</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>394</v>
+        <v>346</v>
       </c>
       <c r="B30" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="C30" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="D30" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E30" t="s">
-        <v>386</v>
+        <v>340</v>
       </c>
       <c r="F30" t="s">
-        <v>395</v>
+        <v>349</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>396</v>
+        <v>364</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>397</v>
+        <v>346</v>
       </c>
       <c r="B31" t="s">
-        <v>398</v>
+        <v>347</v>
       </c>
       <c r="C31" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="D31" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E31" t="s">
-        <v>391</v>
+        <v>340</v>
       </c>
       <c r="F31" t="s">
-        <v>399</v>
+        <v>349</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>400</v>
+        <v>365</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>401</v>
+        <v>346</v>
       </c>
       <c r="B32" t="s">
-        <v>402</v>
+        <v>347</v>
       </c>
       <c r="C32" t="s">
-        <v>323</v>
+        <v>366</v>
       </c>
       <c r="D32" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E32" t="s">
-        <v>403</v>
+        <v>340</v>
       </c>
       <c r="F32" t="s">
-        <v>386</v>
+        <v>349</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>404</v>
+        <v>367</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>405</v>
+        <v>346</v>
       </c>
       <c r="B33" t="s">
-        <v>406</v>
+        <v>347</v>
       </c>
       <c r="C33" t="s">
-        <v>306</v>
+        <v>368</v>
       </c>
       <c r="D33" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E33" t="s">
-        <v>407</v>
+        <v>340</v>
       </c>
       <c r="F33" t="s">
-        <v>408</v>
+        <v>349</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>409</v>
+        <v>369</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>410</v>
+        <v>346</v>
       </c>
       <c r="B34" t="s">
-        <v>411</v>
+        <v>347</v>
       </c>
       <c r="C34" t="s">
-        <v>254</v>
+        <v>370</v>
       </c>
       <c r="D34" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E34" t="s">
-        <v>412</v>
+        <v>340</v>
       </c>
       <c r="F34" t="s">
-        <v>413</v>
+        <v>349</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>414</v>
+        <v>371</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>415</v>
+        <v>346</v>
       </c>
       <c r="B35" t="s">
-        <v>416</v>
+        <v>347</v>
       </c>
       <c r="C35" t="s">
-        <v>277</v>
+        <v>372</v>
       </c>
       <c r="D35" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E35" t="s">
-        <v>417</v>
+        <v>340</v>
       </c>
       <c r="F35" t="s">
-        <v>386</v>
+        <v>349</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>418</v>
+        <v>373</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>419</v>
+        <v>374</v>
       </c>
       <c r="B36" t="s">
-        <v>420</v>
+        <v>271</v>
       </c>
       <c r="C36" t="s">
-        <v>421</v>
+        <v>272</v>
       </c>
       <c r="D36" t="s">
-        <v>335</v>
+        <v>242</v>
       </c>
       <c r="E36" t="s">
-        <v>422</v>
+        <v>375</v>
       </c>
       <c r="F36" t="s">
-        <v>423</v>
+        <v>376</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>424</v>
+        <v>377</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>89</v>
+        <v>378</v>
       </c>
       <c r="B37" t="s">
-        <v>425</v>
+        <v>379</v>
       </c>
       <c r="C37" t="s">
-        <v>426</v>
+        <v>380</v>
       </c>
       <c r="D37" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E37" t="s">
-        <v>307</v>
+        <v>381</v>
       </c>
       <c r="F37" t="s">
-        <v>427</v>
+        <v>382</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>428</v>
+        <v>383</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>89</v>
+        <v>384</v>
       </c>
       <c r="B38" t="s">
-        <v>429</v>
+        <v>385</v>
       </c>
       <c r="C38" t="s">
-        <v>430</v>
+        <v>299</v>
       </c>
       <c r="D38" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E38" t="s">
         <v>386</v>
       </c>
       <c r="F38" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>431</v>
+        <v>388</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>432</v>
+        <v>389</v>
       </c>
       <c r="B39" t="s">
-        <v>433</v>
+        <v>390</v>
       </c>
       <c r="C39" t="s">
-        <v>434</v>
+        <v>391</v>
       </c>
       <c r="D39" t="s">
-        <v>347</v>
+        <v>242</v>
       </c>
       <c r="E39" t="s">
-        <v>435</v>
+        <v>392</v>
       </c>
       <c r="F39" t="s">
-        <v>436</v>
+        <v>393</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>437</v>
+        <v>394</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>438</v>
+        <v>395</v>
       </c>
       <c r="B40" t="s">
-        <v>439</v>
+        <v>396</v>
       </c>
       <c r="C40" t="s">
-        <v>440</v>
+        <v>266</v>
       </c>
       <c r="D40" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E40" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="F40" t="s">
-        <v>441</v>
+        <v>398</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>442</v>
+        <v>399</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>443</v>
+        <v>400</v>
       </c>
       <c r="B41" t="s">
-        <v>444</v>
+        <v>401</v>
       </c>
       <c r="C41" t="s">
-        <v>445</v>
+        <v>402</v>
       </c>
       <c r="D41" t="s">
-        <v>236</v>
+        <v>403</v>
       </c>
       <c r="E41" t="s">
-        <v>446</v>
+        <v>404</v>
       </c>
       <c r="F41" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>448</v>
+        <v>406</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>449</v>
+        <v>407</v>
       </c>
       <c r="B42" t="s">
-        <v>450</v>
+        <v>334</v>
       </c>
       <c r="C42" t="s">
-        <v>323</v>
+        <v>348</v>
       </c>
       <c r="D42" t="s">
-        <v>335</v>
+        <v>242</v>
       </c>
       <c r="E42" t="s">
-        <v>451</v>
+        <v>336</v>
       </c>
       <c r="F42" t="s">
-        <v>308</v>
+        <v>337</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>452</v>
+        <v>408</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>453</v>
+        <v>409</v>
       </c>
       <c r="B43" t="s">
-        <v>454</v>
+        <v>410</v>
       </c>
       <c r="C43" t="s">
-        <v>455</v>
+        <v>411</v>
       </c>
       <c r="D43" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E43" t="s">
-        <v>456</v>
+        <v>412</v>
       </c>
       <c r="F43" t="s">
-        <v>457</v>
+        <v>413</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>458</v>
+        <v>414</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>459</v>
+        <v>415</v>
       </c>
       <c r="B44" t="s">
-        <v>460</v>
+        <v>416</v>
       </c>
       <c r="C44" t="s">
-        <v>461</v>
+        <v>391</v>
       </c>
       <c r="D44" t="s">
-        <v>236</v>
+        <v>403</v>
       </c>
       <c r="E44" t="s">
-        <v>462</v>
+        <v>417</v>
       </c>
       <c r="F44" t="s">
-        <v>463</v>
+        <v>418</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>464</v>
+        <v>419</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>465</v>
+        <v>420</v>
       </c>
       <c r="B45" t="s">
-        <v>466</v>
+        <v>421</v>
       </c>
       <c r="C45" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="D45" t="s">
-        <v>236</v>
+        <v>422</v>
       </c>
       <c r="E45" t="s">
-        <v>467</v>
+        <v>423</v>
       </c>
       <c r="F45" t="s">
-        <v>468</v>
+        <v>424</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>469</v>
+        <v>425</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>470</v>
+        <v>426</v>
       </c>
       <c r="B46" t="s">
-        <v>471</v>
+        <v>334</v>
       </c>
       <c r="C46" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="D46" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E46" t="s">
-        <v>472</v>
+        <v>427</v>
       </c>
       <c r="F46" t="s">
-        <v>473</v>
+        <v>337</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>474</v>
+        <v>428</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>475</v>
+        <v>429</v>
       </c>
       <c r="B47" t="s">
-        <v>476</v>
+        <v>430</v>
       </c>
       <c r="C47" t="s">
-        <v>477</v>
+        <v>431</v>
       </c>
       <c r="D47" t="s">
-        <v>236</v>
+        <v>422</v>
       </c>
       <c r="E47" t="s">
-        <v>478</v>
+        <v>432</v>
       </c>
       <c r="F47" t="s">
-        <v>479</v>
+        <v>433</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>480</v>
+        <v>434</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>481</v>
+        <v>435</v>
       </c>
       <c r="B48" t="s">
-        <v>471</v>
+        <v>436</v>
       </c>
       <c r="C48" t="s">
-        <v>254</v>
+        <v>289</v>
       </c>
       <c r="D48" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E48" t="s">
-        <v>472</v>
+        <v>340</v>
       </c>
       <c r="F48" t="s">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>482</v>
+        <v>438</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>483</v>
+        <v>435</v>
       </c>
       <c r="B49" t="s">
-        <v>484</v>
+        <v>436</v>
       </c>
       <c r="C49" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="D49" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E49" t="s">
-        <v>485</v>
+        <v>340</v>
       </c>
       <c r="F49" t="s">
-        <v>386</v>
+        <v>437</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>486</v>
+        <v>439</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>487</v>
+        <v>440</v>
       </c>
       <c r="B50" t="s">
-        <v>488</v>
+        <v>441</v>
       </c>
       <c r="C50" t="s">
-        <v>489</v>
+        <v>442</v>
       </c>
       <c r="D50" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E50" t="s">
-        <v>490</v>
+        <v>443</v>
       </c>
       <c r="F50" t="s">
-        <v>491</v>
+        <v>444</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>492</v>
+        <v>445</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>493</v>
+        <v>440</v>
       </c>
       <c r="B51" t="s">
-        <v>287</v>
+        <v>446</v>
       </c>
       <c r="C51" t="s">
-        <v>494</v>
+        <v>266</v>
       </c>
       <c r="D51" t="s">
-        <v>236</v>
+        <v>447</v>
       </c>
       <c r="E51" t="s">
-        <v>495</v>
+        <v>448</v>
       </c>
       <c r="F51" t="s">
-        <v>290</v>
+        <v>449</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>496</v>
+        <v>450</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>497</v>
+        <v>451</v>
       </c>
       <c r="B52" t="s">
-        <v>498</v>
+        <v>452</v>
       </c>
       <c r="C52" t="s">
-        <v>254</v>
+        <v>329</v>
       </c>
       <c r="D52" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E52" t="s">
-        <v>499</v>
+        <v>453</v>
       </c>
       <c r="F52" t="s">
-        <v>290</v>
+        <v>454</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>500</v>
+        <v>455</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>501</v>
+        <v>456</v>
       </c>
       <c r="B53" t="s">
-        <v>502</v>
+        <v>457</v>
       </c>
       <c r="C53" t="s">
-        <v>503</v>
+        <v>241</v>
       </c>
       <c r="D53" t="s">
-        <v>335</v>
+        <v>242</v>
       </c>
       <c r="E53" t="s">
-        <v>386</v>
+        <v>458</v>
       </c>
       <c r="F53" t="s">
-        <v>504</v>
+        <v>459</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>505</v>
+        <v>460</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>506</v>
+        <v>461</v>
       </c>
       <c r="B54" t="s">
-        <v>507</v>
+        <v>462</v>
       </c>
       <c r="C54" t="s">
-        <v>254</v>
+        <v>391</v>
       </c>
       <c r="D54" t="s">
-        <v>347</v>
+        <v>242</v>
       </c>
       <c r="E54" t="s">
-        <v>508</v>
+        <v>375</v>
       </c>
       <c r="F54" t="s">
-        <v>509</v>
+        <v>463</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>510</v>
+        <v>464</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>511</v>
+        <v>465</v>
       </c>
       <c r="B55" t="s">
-        <v>512</v>
+        <v>466</v>
       </c>
       <c r="C55" t="s">
-        <v>306</v>
+        <v>266</v>
       </c>
       <c r="D55" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E55" t="s">
-        <v>386</v>
+        <v>467</v>
       </c>
       <c r="F55" t="s">
-        <v>513</v>
+        <v>250</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>514</v>
+        <v>468</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>511</v>
+        <v>469</v>
       </c>
       <c r="B56" t="s">
-        <v>512</v>
+        <v>470</v>
       </c>
       <c r="C56" t="s">
-        <v>515</v>
+        <v>471</v>
       </c>
       <c r="D56" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E56" t="s">
-        <v>386</v>
+        <v>472</v>
       </c>
       <c r="F56" t="s">
-        <v>513</v>
+        <v>274</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>516</v>
+        <v>473</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>511</v>
+        <v>474</v>
       </c>
       <c r="B57" t="s">
-        <v>512</v>
+        <v>475</v>
       </c>
       <c r="C57" t="s">
-        <v>254</v>
+        <v>476</v>
       </c>
       <c r="D57" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E57" t="s">
-        <v>386</v>
+        <v>477</v>
       </c>
       <c r="F57" t="s">
-        <v>513</v>
+        <v>478</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>517</v>
+        <v>479</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>518</v>
+        <v>480</v>
       </c>
       <c r="B58" t="s">
-        <v>519</v>
+        <v>441</v>
       </c>
       <c r="C58" t="s">
-        <v>323</v>
+        <v>442</v>
       </c>
       <c r="D58" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E58" t="s">
-        <v>520</v>
+        <v>274</v>
       </c>
       <c r="F58" t="s">
-        <v>521</v>
+        <v>481</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>522</v>
+        <v>482</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>523</v>
+        <v>483</v>
       </c>
       <c r="B59" t="s">
-        <v>287</v>
+        <v>484</v>
       </c>
       <c r="C59" t="s">
-        <v>524</v>
+        <v>391</v>
       </c>
       <c r="D59" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E59" t="s">
-        <v>525</v>
+        <v>477</v>
       </c>
       <c r="F59" t="s">
-        <v>290</v>
+        <v>485</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>526</v>
+        <v>486</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>527</v>
+        <v>487</v>
       </c>
       <c r="B60" t="s">
-        <v>433</v>
+        <v>488</v>
       </c>
       <c r="C60" t="s">
-        <v>528</v>
+        <v>489</v>
       </c>
       <c r="D60" t="s">
-        <v>347</v>
+        <v>242</v>
       </c>
       <c r="E60" t="s">
-        <v>529</v>
+        <v>490</v>
       </c>
       <c r="F60" t="s">
-        <v>530</v>
+        <v>491</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>531</v>
+        <v>492</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>532</v>
+        <v>493</v>
       </c>
       <c r="B61" t="s">
-        <v>533</v>
+        <v>494</v>
       </c>
       <c r="C61" t="s">
-        <v>534</v>
+        <v>391</v>
       </c>
       <c r="D61" t="s">
-        <v>347</v>
+        <v>242</v>
       </c>
       <c r="E61" t="s">
-        <v>386</v>
+        <v>495</v>
       </c>
       <c r="F61" t="s">
-        <v>535</v>
+        <v>274</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>536</v>
+        <v>496</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>537</v>
+        <v>497</v>
       </c>
       <c r="B62" t="s">
-        <v>538</v>
+        <v>498</v>
       </c>
       <c r="C62" t="s">
-        <v>254</v>
+        <v>329</v>
       </c>
       <c r="D62" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E62" t="s">
-        <v>539</v>
+        <v>499</v>
       </c>
       <c r="F62" t="s">
-        <v>386</v>
+        <v>500</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>540</v>
+        <v>501</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>541</v>
+        <v>502</v>
       </c>
       <c r="B63" t="s">
-        <v>542</v>
+        <v>503</v>
       </c>
       <c r="C63" t="s">
-        <v>543</v>
+        <v>266</v>
       </c>
       <c r="D63" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E63" t="s">
-        <v>386</v>
+        <v>504</v>
       </c>
       <c r="F63" t="s">
-        <v>392</v>
+        <v>505</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>544</v>
+        <v>506</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>545</v>
+        <v>507</v>
       </c>
       <c r="B64" t="s">
-        <v>546</v>
+        <v>436</v>
       </c>
       <c r="C64" t="s">
-        <v>547</v>
+        <v>356</v>
       </c>
       <c r="D64" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E64" t="s">
-        <v>548</v>
+        <v>427</v>
       </c>
       <c r="F64" t="s">
-        <v>549</v>
+        <v>337</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>550</v>
+        <v>508</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>551</v>
+        <v>509</v>
       </c>
       <c r="B65" t="s">
-        <v>552</v>
+        <v>510</v>
       </c>
       <c r="C65" t="s">
-        <v>553</v>
+        <v>511</v>
       </c>
       <c r="D65" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E65" t="s">
-        <v>386</v>
+        <v>512</v>
       </c>
       <c r="F65" t="s">
-        <v>554</v>
+        <v>337</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>555</v>
+        <v>513</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>556</v>
+        <v>509</v>
       </c>
       <c r="B66" t="s">
-        <v>557</v>
+        <v>510</v>
       </c>
       <c r="C66" t="s">
-        <v>558</v>
+        <v>514</v>
       </c>
       <c r="D66" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E66" t="s">
-        <v>559</v>
+        <v>512</v>
       </c>
       <c r="F66" t="s">
-        <v>560</v>
+        <v>337</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>561</v>
+        <v>515</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>562</v>
+        <v>509</v>
       </c>
       <c r="B67" t="s">
-        <v>563</v>
+        <v>510</v>
       </c>
       <c r="C67" t="s">
-        <v>323</v>
+        <v>342</v>
       </c>
       <c r="D67" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E67" t="s">
-        <v>564</v>
+        <v>512</v>
       </c>
       <c r="F67" t="s">
-        <v>565</v>
+        <v>337</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>566</v>
+        <v>516</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>567</v>
+        <v>509</v>
       </c>
       <c r="B68" t="s">
-        <v>568</v>
+        <v>510</v>
       </c>
       <c r="C68" t="s">
-        <v>569</v>
+        <v>517</v>
       </c>
       <c r="D68" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E68" t="s">
-        <v>570</v>
+        <v>512</v>
       </c>
       <c r="F68" t="s">
-        <v>436</v>
+        <v>337</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>571</v>
+        <v>518</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>572</v>
+        <v>509</v>
       </c>
       <c r="B69" t="s">
-        <v>568</v>
+        <v>510</v>
       </c>
       <c r="C69" t="s">
-        <v>573</v>
+        <v>329</v>
       </c>
       <c r="D69" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E69" t="s">
-        <v>574</v>
+        <v>512</v>
       </c>
       <c r="F69" t="s">
-        <v>392</v>
+        <v>337</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>575</v>
+        <v>519</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>576</v>
+        <v>509</v>
       </c>
       <c r="B70" t="s">
-        <v>577</v>
+        <v>510</v>
       </c>
       <c r="C70" t="s">
-        <v>578</v>
+        <v>520</v>
       </c>
       <c r="D70" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E70" t="s">
-        <v>579</v>
+        <v>512</v>
       </c>
       <c r="F70" t="s">
-        <v>580</v>
+        <v>337</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>581</v>
+        <v>521</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>582</v>
+        <v>509</v>
       </c>
       <c r="B71" t="s">
-        <v>583</v>
+        <v>510</v>
       </c>
       <c r="C71" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="D71" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E71" t="s">
-        <v>584</v>
+        <v>512</v>
       </c>
       <c r="F71" t="s">
-        <v>585</v>
+        <v>337</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>586</v>
+        <v>523</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>587</v>
+        <v>509</v>
       </c>
       <c r="B72" t="s">
-        <v>588</v>
+        <v>510</v>
       </c>
       <c r="C72" t="s">
-        <v>323</v>
+        <v>524</v>
       </c>
       <c r="D72" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E72" t="s">
-        <v>589</v>
+        <v>512</v>
       </c>
       <c r="F72" t="s">
-        <v>590</v>
+        <v>337</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>591</v>
+        <v>525</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>592</v>
+        <v>509</v>
       </c>
       <c r="B73" t="s">
-        <v>593</v>
+        <v>510</v>
       </c>
       <c r="C73" t="s">
-        <v>254</v>
+        <v>526</v>
       </c>
       <c r="D73" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E73" t="s">
-        <v>594</v>
+        <v>512</v>
       </c>
       <c r="F73" t="s">
-        <v>366</v>
+        <v>337</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>595</v>
+        <v>527</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>596</v>
+        <v>509</v>
       </c>
       <c r="B74" t="s">
-        <v>597</v>
+        <v>510</v>
       </c>
       <c r="C74" t="s">
-        <v>254</v>
+        <v>528</v>
       </c>
       <c r="D74" t="s">
-        <v>598</v>
+        <v>242</v>
       </c>
       <c r="E74" t="s">
-        <v>599</v>
+        <v>512</v>
       </c>
       <c r="F74" t="s">
-        <v>600</v>
+        <v>337</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>601</v>
+        <v>529</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>602</v>
+        <v>530</v>
       </c>
       <c r="B75" t="s">
-        <v>603</v>
+        <v>531</v>
       </c>
       <c r="C75" t="s">
-        <v>604</v>
+        <v>295</v>
       </c>
       <c r="D75" t="s">
-        <v>598</v>
+        <v>242</v>
       </c>
       <c r="E75" t="s">
-        <v>605</v>
+        <v>532</v>
       </c>
       <c r="F75" t="s">
-        <v>606</v>
+        <v>274</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>607</v>
+        <v>533</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>608</v>
+        <v>534</v>
       </c>
       <c r="B76" t="s">
-        <v>609</v>
+        <v>535</v>
       </c>
       <c r="C76" t="s">
-        <v>323</v>
+        <v>536</v>
       </c>
       <c r="D76" t="s">
-        <v>236</v>
+        <v>403</v>
       </c>
       <c r="E76" t="s">
-        <v>610</v>
+        <v>537</v>
       </c>
       <c r="F76" t="s">
-        <v>611</v>
+        <v>538</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>612</v>
+        <v>539</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>613</v>
+        <v>89</v>
       </c>
       <c r="B77" t="s">
-        <v>614</v>
+        <v>540</v>
       </c>
       <c r="C77" t="s">
-        <v>254</v>
+        <v>541</v>
       </c>
       <c r="D77" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E77" t="s">
-        <v>615</v>
+        <v>330</v>
       </c>
       <c r="F77" t="s">
-        <v>386</v>
+        <v>542</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>616</v>
+        <v>543</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>617</v>
+        <v>89</v>
       </c>
       <c r="B78" t="s">
-        <v>618</v>
+        <v>544</v>
       </c>
       <c r="C78" t="s">
-        <v>306</v>
+        <v>342</v>
       </c>
       <c r="D78" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E78" t="s">
-        <v>619</v>
+        <v>274</v>
       </c>
       <c r="F78" t="s">
-        <v>620</v>
+        <v>274</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>621</v>
+        <v>545</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>622</v>
+        <v>546</v>
       </c>
       <c r="B79" t="s">
-        <v>623</v>
+        <v>547</v>
       </c>
       <c r="C79" t="s">
-        <v>254</v>
+        <v>368</v>
       </c>
       <c r="D79" t="s">
-        <v>624</v>
+        <v>242</v>
       </c>
       <c r="E79" t="s">
-        <v>625</v>
+        <v>548</v>
       </c>
       <c r="F79" t="s">
-        <v>386</v>
+        <v>491</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>626</v>
+        <v>549</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>627</v>
+        <v>550</v>
       </c>
       <c r="B80" t="s">
-        <v>628</v>
+        <v>551</v>
       </c>
       <c r="C80" t="s">
-        <v>629</v>
+        <v>552</v>
       </c>
       <c r="D80" t="s">
-        <v>236</v>
+        <v>422</v>
       </c>
       <c r="E80" t="s">
-        <v>630</v>
+        <v>553</v>
       </c>
       <c r="F80" t="s">
-        <v>631</v>
+        <v>554</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>632</v>
+        <v>555</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>633</v>
+        <v>556</v>
       </c>
       <c r="B81" t="s">
-        <v>634</v>
+        <v>557</v>
       </c>
       <c r="C81" t="s">
-        <v>353</v>
+        <v>558</v>
       </c>
       <c r="D81" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E81" t="s">
-        <v>386</v>
+        <v>477</v>
       </c>
       <c r="F81" t="s">
-        <v>635</v>
+        <v>559</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>636</v>
+        <v>560</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>633</v>
+        <v>561</v>
       </c>
       <c r="B82" t="s">
-        <v>634</v>
+        <v>562</v>
       </c>
       <c r="C82" t="s">
-        <v>637</v>
+        <v>563</v>
       </c>
       <c r="D82" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E82" t="s">
-        <v>386</v>
+        <v>564</v>
       </c>
       <c r="F82" t="s">
-        <v>635</v>
+        <v>565</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>638</v>
+        <v>566</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>639</v>
+        <v>567</v>
       </c>
       <c r="B83" t="s">
-        <v>640</v>
+        <v>568</v>
       </c>
       <c r="C83" t="s">
-        <v>641</v>
+        <v>391</v>
       </c>
       <c r="D83" t="s">
-        <v>236</v>
+        <v>403</v>
       </c>
       <c r="E83" t="s">
-        <v>642</v>
+        <v>569</v>
       </c>
       <c r="F83" t="s">
-        <v>386</v>
+        <v>331</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>643</v>
+        <v>570</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>644</v>
+        <v>571</v>
       </c>
       <c r="B84" t="s">
-        <v>645</v>
+        <v>572</v>
       </c>
       <c r="C84" t="s">
-        <v>534</v>
+        <v>573</v>
       </c>
       <c r="D84" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E84" t="s">
-        <v>386</v>
+        <v>574</v>
       </c>
       <c r="F84" t="s">
-        <v>386</v>
+        <v>575</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>646</v>
+        <v>576</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>647</v>
+        <v>577</v>
       </c>
       <c r="B85" t="s">
-        <v>648</v>
+        <v>316</v>
       </c>
       <c r="C85" t="s">
-        <v>649</v>
+        <v>578</v>
       </c>
       <c r="D85" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E85" t="s">
-        <v>255</v>
+        <v>579</v>
       </c>
       <c r="F85" t="s">
-        <v>650</v>
+        <v>580</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>651</v>
+        <v>581</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>652</v>
+        <v>582</v>
       </c>
       <c r="B86" t="s">
-        <v>653</v>
+        <v>583</v>
       </c>
       <c r="C86" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="D86" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E86" t="s">
-        <v>654</v>
+        <v>584</v>
       </c>
       <c r="F86" t="s">
-        <v>655</v>
+        <v>585</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>656</v>
+        <v>586</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>657</v>
+        <v>587</v>
       </c>
       <c r="B87" t="s">
-        <v>658</v>
+        <v>588</v>
       </c>
       <c r="C87" t="s">
-        <v>659</v>
+        <v>266</v>
       </c>
       <c r="D87" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E87" t="s">
-        <v>660</v>
+        <v>589</v>
       </c>
       <c r="F87" t="s">
-        <v>661</v>
+        <v>491</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>662</v>
+        <v>590</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>663</v>
+        <v>591</v>
       </c>
       <c r="B88" t="s">
-        <v>293</v>
+        <v>592</v>
       </c>
       <c r="C88" t="s">
-        <v>664</v>
+        <v>593</v>
       </c>
       <c r="D88" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E88" t="s">
-        <v>295</v>
+        <v>594</v>
       </c>
       <c r="F88" t="s">
-        <v>296</v>
+        <v>595</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>665</v>
+        <v>596</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>666</v>
+        <v>597</v>
       </c>
       <c r="B89" t="s">
-        <v>667</v>
+        <v>588</v>
       </c>
       <c r="C89" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="D89" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E89" t="s">
-        <v>668</v>
+        <v>589</v>
       </c>
       <c r="F89" t="s">
-        <v>669</v>
+        <v>491</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>670</v>
+        <v>598</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>671</v>
+        <v>599</v>
       </c>
       <c r="B90" t="s">
-        <v>672</v>
+        <v>600</v>
       </c>
       <c r="C90" t="s">
-        <v>673</v>
+        <v>266</v>
       </c>
       <c r="D90" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E90" t="s">
-        <v>674</v>
+        <v>601</v>
       </c>
       <c r="F90" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>675</v>
+        <v>602</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>676</v>
+        <v>603</v>
       </c>
       <c r="B91" t="s">
-        <v>677</v>
+        <v>604</v>
       </c>
       <c r="C91" t="s">
-        <v>254</v>
+        <v>605</v>
       </c>
       <c r="D91" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E91" t="s">
-        <v>678</v>
+        <v>606</v>
       </c>
       <c r="F91" t="s">
-        <v>679</v>
+        <v>607</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>680</v>
+        <v>608</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>681</v>
+        <v>609</v>
       </c>
       <c r="B92" t="s">
-        <v>677</v>
+        <v>304</v>
       </c>
       <c r="C92" t="s">
-        <v>254</v>
+        <v>610</v>
       </c>
       <c r="D92" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E92" t="s">
-        <v>678</v>
+        <v>611</v>
       </c>
       <c r="F92" t="s">
-        <v>682</v>
+        <v>307</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>683</v>
+        <v>612</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>684</v>
+        <v>613</v>
       </c>
       <c r="B93" t="s">
-        <v>685</v>
+        <v>614</v>
       </c>
       <c r="C93" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="D93" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E93" t="s">
-        <v>386</v>
+        <v>615</v>
       </c>
       <c r="F93" t="s">
-        <v>366</v>
+        <v>307</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>686</v>
+        <v>616</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>687</v>
+        <v>617</v>
       </c>
       <c r="B94" t="s">
-        <v>688</v>
+        <v>618</v>
       </c>
       <c r="C94" t="s">
-        <v>689</v>
+        <v>372</v>
       </c>
       <c r="D94" t="s">
-        <v>335</v>
+        <v>403</v>
       </c>
       <c r="E94" t="s">
-        <v>386</v>
+        <v>274</v>
       </c>
       <c r="F94" t="s">
-        <v>690</v>
+        <v>619</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>691</v>
+        <v>620</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>692</v>
+        <v>621</v>
       </c>
       <c r="B95" t="s">
-        <v>693</v>
+        <v>622</v>
       </c>
       <c r="C95" t="s">
-        <v>477</v>
+        <v>266</v>
       </c>
       <c r="D95" t="s">
-        <v>236</v>
+        <v>422</v>
       </c>
       <c r="E95" t="s">
-        <v>694</v>
+        <v>623</v>
       </c>
       <c r="F95" t="s">
-        <v>695</v>
+        <v>624</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>696</v>
+        <v>625</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>697</v>
+        <v>626</v>
       </c>
       <c r="B96" t="s">
-        <v>698</v>
+        <v>627</v>
       </c>
       <c r="C96" t="s">
-        <v>254</v>
+        <v>329</v>
       </c>
       <c r="D96" t="s">
-        <v>347</v>
+        <v>242</v>
       </c>
       <c r="E96" t="s">
-        <v>699</v>
+        <v>274</v>
       </c>
       <c r="F96" t="s">
-        <v>700</v>
+        <v>628</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>701</v>
+        <v>629</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>702</v>
+        <v>626</v>
       </c>
       <c r="B97" t="s">
-        <v>563</v>
+        <v>627</v>
       </c>
       <c r="C97" t="s">
-        <v>703</v>
+        <v>630</v>
       </c>
       <c r="D97" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E97" t="s">
-        <v>704</v>
+        <v>274</v>
       </c>
       <c r="F97" t="s">
-        <v>565</v>
+        <v>628</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>705</v>
+        <v>631</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>706</v>
+        <v>626</v>
       </c>
       <c r="B98" t="s">
-        <v>460</v>
+        <v>627</v>
       </c>
       <c r="C98" t="s">
-        <v>707</v>
+        <v>266</v>
       </c>
       <c r="D98" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E98" t="s">
-        <v>462</v>
+        <v>274</v>
       </c>
       <c r="F98" t="s">
-        <v>708</v>
+        <v>628</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>709</v>
+        <v>632</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>710</v>
+        <v>633</v>
       </c>
       <c r="B99" t="s">
-        <v>711</v>
+        <v>634</v>
       </c>
       <c r="C99" t="s">
-        <v>430</v>
+        <v>329</v>
       </c>
       <c r="D99" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E99" t="s">
-        <v>712</v>
+        <v>635</v>
       </c>
       <c r="F99" t="s">
-        <v>713</v>
+        <v>636</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>714</v>
+        <v>637</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>715</v>
+        <v>638</v>
       </c>
       <c r="B100" t="s">
-        <v>716</v>
+        <v>639</v>
       </c>
       <c r="C100" t="s">
-        <v>717</v>
+        <v>640</v>
       </c>
       <c r="D100" t="s">
-        <v>347</v>
+        <v>242</v>
       </c>
       <c r="E100" t="s">
-        <v>718</v>
+        <v>641</v>
       </c>
       <c r="F100" t="s">
-        <v>719</v>
+        <v>491</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>720</v>
+        <v>642</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>715</v>
+        <v>643</v>
       </c>
       <c r="B101" t="s">
-        <v>721</v>
+        <v>644</v>
       </c>
       <c r="C101" t="s">
-        <v>722</v>
+        <v>391</v>
       </c>
       <c r="D101" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E101" t="s">
-        <v>723</v>
+        <v>645</v>
       </c>
       <c r="F101" t="s">
-        <v>724</v>
+        <v>646</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>725</v>
+        <v>647</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>726</v>
+        <v>648</v>
       </c>
       <c r="B102" t="s">
-        <v>716</v>
+        <v>304</v>
       </c>
       <c r="C102" t="s">
-        <v>717</v>
+        <v>649</v>
       </c>
       <c r="D102" t="s">
-        <v>347</v>
+        <v>242</v>
       </c>
       <c r="E102" t="s">
-        <v>718</v>
+        <v>650</v>
       </c>
       <c r="F102" t="s">
-        <v>719</v>
+        <v>307</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>727</v>
+        <v>651</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>652</v>
+      </c>
+      <c r="B103" t="s">
+        <v>551</v>
+      </c>
+      <c r="C103" t="s">
+        <v>653</v>
+      </c>
+      <c r="D103" t="s">
+        <v>422</v>
+      </c>
+      <c r="E103" t="s">
+        <v>654</v>
+      </c>
+      <c r="F103" t="s">
+        <v>655</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>657</v>
+      </c>
+      <c r="B104" t="s">
+        <v>658</v>
+      </c>
+      <c r="C104" t="s">
+        <v>356</v>
+      </c>
+      <c r="D104" t="s">
+        <v>422</v>
+      </c>
+      <c r="E104" t="s">
+        <v>274</v>
+      </c>
+      <c r="F104" t="s">
+        <v>659</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>661</v>
+      </c>
+      <c r="B105" t="s">
+        <v>662</v>
+      </c>
+      <c r="C105" t="s">
+        <v>266</v>
+      </c>
+      <c r="D105" t="s">
+        <v>242</v>
+      </c>
+      <c r="E105" t="s">
+        <v>663</v>
+      </c>
+      <c r="F105" t="s">
+        <v>274</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>665</v>
+      </c>
+      <c r="B106" t="s">
+        <v>666</v>
+      </c>
+      <c r="C106" t="s">
+        <v>348</v>
+      </c>
+      <c r="D106" t="s">
+        <v>242</v>
+      </c>
+      <c r="E106" t="s">
+        <v>274</v>
+      </c>
+      <c r="F106" t="s">
+        <v>478</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>668</v>
+      </c>
+      <c r="B107" t="s">
+        <v>669</v>
+      </c>
+      <c r="C107" t="s">
+        <v>670</v>
+      </c>
+      <c r="D107" t="s">
+        <v>242</v>
+      </c>
+      <c r="E107" t="s">
+        <v>671</v>
+      </c>
+      <c r="F107" t="s">
+        <v>672</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>674</v>
+      </c>
+      <c r="B108" t="s">
+        <v>675</v>
+      </c>
+      <c r="C108" t="s">
+        <v>676</v>
+      </c>
+      <c r="D108" t="s">
+        <v>242</v>
+      </c>
+      <c r="E108" t="s">
+        <v>274</v>
+      </c>
+      <c r="F108" t="s">
+        <v>677</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>679</v>
+      </c>
+      <c r="B109" t="s">
+        <v>680</v>
+      </c>
+      <c r="C109" t="s">
+        <v>681</v>
+      </c>
+      <c r="D109" t="s">
+        <v>242</v>
+      </c>
+      <c r="E109" t="s">
+        <v>682</v>
+      </c>
+      <c r="F109" t="s">
+        <v>683</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>685</v>
+      </c>
+      <c r="B110" t="s">
+        <v>686</v>
+      </c>
+      <c r="C110" t="s">
+        <v>391</v>
+      </c>
+      <c r="D110" t="s">
+        <v>242</v>
+      </c>
+      <c r="E110" t="s">
+        <v>687</v>
+      </c>
+      <c r="F110" t="s">
+        <v>688</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>690</v>
+      </c>
+      <c r="B111" t="s">
+        <v>436</v>
+      </c>
+      <c r="C111" t="s">
+        <v>517</v>
+      </c>
+      <c r="D111" t="s">
+        <v>242</v>
+      </c>
+      <c r="E111" t="s">
+        <v>691</v>
+      </c>
+      <c r="F111" t="s">
+        <v>692</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>694</v>
+      </c>
+      <c r="B112" t="s">
+        <v>334</v>
+      </c>
+      <c r="C112" t="s">
+        <v>370</v>
+      </c>
+      <c r="D112" t="s">
+        <v>242</v>
+      </c>
+      <c r="E112" t="s">
+        <v>427</v>
+      </c>
+      <c r="F112" t="s">
+        <v>337</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>696</v>
+      </c>
+      <c r="B113" t="s">
+        <v>697</v>
+      </c>
+      <c r="C113" t="s">
+        <v>698</v>
+      </c>
+      <c r="D113" t="s">
+        <v>242</v>
+      </c>
+      <c r="E113" t="s">
+        <v>699</v>
+      </c>
+      <c r="F113" t="s">
+        <v>554</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>701</v>
+      </c>
+      <c r="B114" t="s">
+        <v>697</v>
+      </c>
+      <c r="C114" t="s">
+        <v>702</v>
+      </c>
+      <c r="D114" t="s">
+        <v>242</v>
+      </c>
+      <c r="E114" t="s">
+        <v>703</v>
+      </c>
+      <c r="F114" t="s">
+        <v>478</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>705</v>
+      </c>
+      <c r="B115" t="s">
+        <v>706</v>
+      </c>
+      <c r="C115" t="s">
+        <v>335</v>
+      </c>
+      <c r="D115" t="s">
+        <v>447</v>
+      </c>
+      <c r="E115" t="s">
+        <v>707</v>
+      </c>
+      <c r="F115" t="s">
+        <v>708</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>710</v>
+      </c>
+      <c r="B116" t="s">
+        <v>711</v>
+      </c>
+      <c r="C116" t="s">
+        <v>712</v>
+      </c>
+      <c r="D116" t="s">
+        <v>242</v>
+      </c>
+      <c r="E116" t="s">
+        <v>713</v>
+      </c>
+      <c r="F116" t="s">
+        <v>714</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>716</v>
+      </c>
+      <c r="B117" t="s">
+        <v>717</v>
+      </c>
+      <c r="C117" t="s">
+        <v>356</v>
+      </c>
+      <c r="D117" t="s">
+        <v>242</v>
+      </c>
+      <c r="E117" t="s">
+        <v>718</v>
+      </c>
+      <c r="F117" t="s">
+        <v>719</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>721</v>
+      </c>
+      <c r="B118" t="s">
+        <v>722</v>
+      </c>
+      <c r="C118" t="s">
+        <v>489</v>
+      </c>
+      <c r="D118" t="s">
+        <v>723</v>
+      </c>
+      <c r="E118" t="s">
+        <v>724</v>
+      </c>
+      <c r="F118" t="s">
+        <v>725</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>727</v>
+      </c>
+      <c r="B119" t="s">
         <v>728</v>
       </c>
-      <c r="B103" t="s">
-        <v>716</v>
-      </c>
-      <c r="C103" t="s">
-        <v>717</v>
-      </c>
-      <c r="D103" t="s">
-        <v>347</v>
-      </c>
-      <c r="E103" t="s">
-        <v>718</v>
-      </c>
-      <c r="F103" t="s">
-        <v>719</v>
-      </c>
-      <c r="H103" s="2" t="s">
+      <c r="C119" t="s">
+        <v>391</v>
+      </c>
+      <c r="D119" t="s">
+        <v>242</v>
+      </c>
+      <c r="E119" t="s">
         <v>729</v>
+      </c>
+      <c r="F119" t="s">
+        <v>730</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>732</v>
+      </c>
+      <c r="B120" t="s">
+        <v>733</v>
+      </c>
+      <c r="C120" t="s">
+        <v>266</v>
+      </c>
+      <c r="D120" t="s">
+        <v>242</v>
+      </c>
+      <c r="E120" t="s">
+        <v>734</v>
+      </c>
+      <c r="F120" t="s">
+        <v>454</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>736</v>
+      </c>
+      <c r="B121" t="s">
+        <v>737</v>
+      </c>
+      <c r="C121" t="s">
+        <v>738</v>
+      </c>
+      <c r="D121" t="s">
+        <v>422</v>
+      </c>
+      <c r="E121" t="s">
+        <v>739</v>
+      </c>
+      <c r="F121" t="s">
+        <v>740</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>742</v>
+      </c>
+      <c r="B122" t="s">
+        <v>743</v>
+      </c>
+      <c r="C122" t="s">
+        <v>266</v>
+      </c>
+      <c r="D122" t="s">
+        <v>447</v>
+      </c>
+      <c r="E122" t="s">
+        <v>744</v>
+      </c>
+      <c r="F122" t="s">
+        <v>745</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>747</v>
+      </c>
+      <c r="B123" t="s">
+        <v>748</v>
+      </c>
+      <c r="C123" t="s">
+        <v>749</v>
+      </c>
+      <c r="D123" t="s">
+        <v>447</v>
+      </c>
+      <c r="E123" t="s">
+        <v>750</v>
+      </c>
+      <c r="F123" t="s">
+        <v>751</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>753</v>
+      </c>
+      <c r="B124" t="s">
+        <v>754</v>
+      </c>
+      <c r="C124" t="s">
+        <v>391</v>
+      </c>
+      <c r="D124" t="s">
+        <v>242</v>
+      </c>
+      <c r="E124" t="s">
+        <v>755</v>
+      </c>
+      <c r="F124" t="s">
+        <v>756</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>758</v>
+      </c>
+      <c r="B125" t="s">
+        <v>759</v>
+      </c>
+      <c r="C125" t="s">
+        <v>266</v>
+      </c>
+      <c r="D125" t="s">
+        <v>242</v>
+      </c>
+      <c r="E125" t="s">
+        <v>760</v>
+      </c>
+      <c r="F125" t="s">
+        <v>274</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>762</v>
+      </c>
+      <c r="B126" t="s">
+        <v>316</v>
+      </c>
+      <c r="C126" t="s">
+        <v>317</v>
+      </c>
+      <c r="D126" t="s">
+        <v>242</v>
+      </c>
+      <c r="E126" t="s">
+        <v>318</v>
+      </c>
+      <c r="F126" t="s">
+        <v>319</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>764</v>
+      </c>
+      <c r="B127" t="s">
+        <v>765</v>
+      </c>
+      <c r="C127" t="s">
+        <v>329</v>
+      </c>
+      <c r="D127" t="s">
+        <v>242</v>
+      </c>
+      <c r="E127" t="s">
+        <v>766</v>
+      </c>
+      <c r="F127" t="s">
+        <v>767</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>769</v>
+      </c>
+      <c r="B128" t="s">
+        <v>770</v>
+      </c>
+      <c r="C128" t="s">
+        <v>771</v>
+      </c>
+      <c r="D128" t="s">
+        <v>403</v>
+      </c>
+      <c r="E128" t="s">
+        <v>772</v>
+      </c>
+      <c r="F128" t="s">
+        <v>773</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>775</v>
+      </c>
+      <c r="B129" t="s">
+        <v>271</v>
+      </c>
+      <c r="C129" t="s">
+        <v>272</v>
+      </c>
+      <c r="D129" t="s">
+        <v>242</v>
+      </c>
+      <c r="E129" t="s">
+        <v>776</v>
+      </c>
+      <c r="F129" t="s">
+        <v>376</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>778</v>
+      </c>
+      <c r="B130" t="s">
+        <v>779</v>
+      </c>
+      <c r="C130" t="s">
+        <v>266</v>
+      </c>
+      <c r="D130" t="s">
+        <v>723</v>
+      </c>
+      <c r="E130" t="s">
+        <v>336</v>
+      </c>
+      <c r="F130" t="s">
+        <v>274</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>233</v>
+      </c>
+      <c r="B131" t="s">
+        <v>234</v>
+      </c>
+      <c r="C131" t="s">
+        <v>489</v>
+      </c>
+      <c r="D131" t="s">
+        <v>242</v>
+      </c>
+      <c r="E131" t="s">
+        <v>781</v>
+      </c>
+      <c r="F131" t="s">
+        <v>782</v>
+      </c>
+      <c r="G131" t="s">
+        <v>783</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>785</v>
+      </c>
+      <c r="B132" t="s">
+        <v>786</v>
+      </c>
+      <c r="C132" t="s">
+        <v>431</v>
+      </c>
+      <c r="D132" t="s">
+        <v>242</v>
+      </c>
+      <c r="E132" t="s">
+        <v>274</v>
+      </c>
+      <c r="F132" t="s">
+        <v>787</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>785</v>
+      </c>
+      <c r="B133" t="s">
+        <v>786</v>
+      </c>
+      <c r="C133" t="s">
+        <v>789</v>
+      </c>
+      <c r="D133" t="s">
+        <v>242</v>
+      </c>
+      <c r="E133" t="s">
+        <v>274</v>
+      </c>
+      <c r="F133" t="s">
+        <v>787</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>791</v>
+      </c>
+      <c r="B134" t="s">
+        <v>786</v>
+      </c>
+      <c r="C134" t="s">
+        <v>431</v>
+      </c>
+      <c r="D134" t="s">
+        <v>242</v>
+      </c>
+      <c r="E134" t="s">
+        <v>274</v>
+      </c>
+      <c r="F134" t="s">
+        <v>787</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>791</v>
+      </c>
+      <c r="B135" t="s">
+        <v>786</v>
+      </c>
+      <c r="C135" t="s">
+        <v>789</v>
+      </c>
+      <c r="D135" t="s">
+        <v>242</v>
+      </c>
+      <c r="E135" t="s">
+        <v>274</v>
+      </c>
+      <c r="F135" t="s">
+        <v>787</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>794</v>
+      </c>
+      <c r="B136" t="s">
+        <v>795</v>
+      </c>
+      <c r="C136" t="s">
+        <v>796</v>
+      </c>
+      <c r="D136" t="s">
+        <v>242</v>
+      </c>
+      <c r="E136" t="s">
+        <v>797</v>
+      </c>
+      <c r="F136" t="s">
+        <v>274</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>799</v>
+      </c>
+      <c r="B137" t="s">
+        <v>800</v>
+      </c>
+      <c r="C137" t="s">
+        <v>356</v>
+      </c>
+      <c r="D137" t="s">
+        <v>242</v>
+      </c>
+      <c r="E137" t="s">
+        <v>274</v>
+      </c>
+      <c r="F137" t="s">
+        <v>274</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>802</v>
+      </c>
+      <c r="B138" t="s">
+        <v>803</v>
+      </c>
+      <c r="C138" t="s">
+        <v>804</v>
+      </c>
+      <c r="D138" t="s">
+        <v>242</v>
+      </c>
+      <c r="E138" t="s">
+        <v>805</v>
+      </c>
+      <c r="F138" t="s">
+        <v>806</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>808</v>
+      </c>
+      <c r="B139" t="s">
+        <v>809</v>
+      </c>
+      <c r="C139" t="s">
+        <v>810</v>
+      </c>
+      <c r="D139" t="s">
+        <v>242</v>
+      </c>
+      <c r="E139" t="s">
+        <v>267</v>
+      </c>
+      <c r="F139" t="s">
+        <v>811</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>813</v>
+      </c>
+      <c r="B140" t="s">
+        <v>814</v>
+      </c>
+      <c r="C140" t="s">
+        <v>241</v>
+      </c>
+      <c r="D140" t="s">
+        <v>242</v>
+      </c>
+      <c r="E140" t="s">
+        <v>815</v>
+      </c>
+      <c r="F140" t="s">
+        <v>816</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>818</v>
+      </c>
+      <c r="B141" t="s">
+        <v>819</v>
+      </c>
+      <c r="C141" t="s">
+        <v>248</v>
+      </c>
+      <c r="D141" t="s">
+        <v>242</v>
+      </c>
+      <c r="E141" t="s">
+        <v>820</v>
+      </c>
+      <c r="F141" t="s">
+        <v>821</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>823</v>
+      </c>
+      <c r="B142" t="s">
+        <v>824</v>
+      </c>
+      <c r="C142" t="s">
+        <v>825</v>
+      </c>
+      <c r="D142" t="s">
+        <v>242</v>
+      </c>
+      <c r="E142" t="s">
+        <v>826</v>
+      </c>
+      <c r="F142" t="s">
+        <v>827</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>829</v>
+      </c>
+      <c r="B143" t="s">
+        <v>830</v>
+      </c>
+      <c r="C143" t="s">
+        <v>391</v>
+      </c>
+      <c r="D143" t="s">
+        <v>242</v>
+      </c>
+      <c r="E143" t="s">
+        <v>831</v>
+      </c>
+      <c r="F143" t="s">
+        <v>832</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>834</v>
+      </c>
+      <c r="B144" t="s">
+        <v>310</v>
+      </c>
+      <c r="C144" t="s">
+        <v>835</v>
+      </c>
+      <c r="D144" t="s">
+        <v>242</v>
+      </c>
+      <c r="E144" t="s">
+        <v>312</v>
+      </c>
+      <c r="F144" t="s">
+        <v>313</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>837</v>
+      </c>
+      <c r="B145" t="s">
+        <v>838</v>
+      </c>
+      <c r="C145" t="s">
+        <v>266</v>
+      </c>
+      <c r="D145" t="s">
+        <v>242</v>
+      </c>
+      <c r="E145" t="s">
+        <v>839</v>
+      </c>
+      <c r="F145" t="s">
+        <v>840</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>842</v>
+      </c>
+      <c r="B146" t="s">
+        <v>843</v>
+      </c>
+      <c r="C146" t="s">
+        <v>844</v>
+      </c>
+      <c r="D146" t="s">
+        <v>242</v>
+      </c>
+      <c r="E146" t="s">
+        <v>845</v>
+      </c>
+      <c r="F146" t="s">
+        <v>301</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>847</v>
+      </c>
+      <c r="B147" t="s">
+        <v>848</v>
+      </c>
+      <c r="C147" t="s">
+        <v>266</v>
+      </c>
+      <c r="D147" t="s">
+        <v>242</v>
+      </c>
+      <c r="E147" t="s">
+        <v>849</v>
+      </c>
+      <c r="F147" t="s">
+        <v>850</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>852</v>
+      </c>
+      <c r="B148" t="s">
+        <v>848</v>
+      </c>
+      <c r="C148" t="s">
+        <v>266</v>
+      </c>
+      <c r="D148" t="s">
+        <v>242</v>
+      </c>
+      <c r="E148" t="s">
+        <v>849</v>
+      </c>
+      <c r="F148" t="s">
+        <v>853</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>855</v>
+      </c>
+      <c r="B149" t="s">
+        <v>830</v>
+      </c>
+      <c r="C149" t="s">
+        <v>391</v>
+      </c>
+      <c r="D149" t="s">
+        <v>242</v>
+      </c>
+      <c r="E149" t="s">
+        <v>856</v>
+      </c>
+      <c r="F149" t="s">
+        <v>832</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>858</v>
+      </c>
+      <c r="B150" t="s">
+        <v>859</v>
+      </c>
+      <c r="C150" t="s">
+        <v>266</v>
+      </c>
+      <c r="D150" t="s">
+        <v>242</v>
+      </c>
+      <c r="E150" t="s">
+        <v>274</v>
+      </c>
+      <c r="F150" t="s">
+        <v>454</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>861</v>
+      </c>
+      <c r="B151" t="s">
+        <v>862</v>
+      </c>
+      <c r="C151" t="s">
+        <v>863</v>
+      </c>
+      <c r="D151" t="s">
+        <v>403</v>
+      </c>
+      <c r="E151" t="s">
+        <v>274</v>
+      </c>
+      <c r="F151" t="s">
+        <v>864</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>866</v>
+      </c>
+      <c r="B152" t="s">
+        <v>867</v>
+      </c>
+      <c r="C152" t="s">
+        <v>593</v>
+      </c>
+      <c r="D152" t="s">
+        <v>242</v>
+      </c>
+      <c r="E152" t="s">
+        <v>868</v>
+      </c>
+      <c r="F152" t="s">
+        <v>869</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>871</v>
+      </c>
+      <c r="B153" t="s">
+        <v>872</v>
+      </c>
+      <c r="C153" t="s">
+        <v>266</v>
+      </c>
+      <c r="D153" t="s">
+        <v>422</v>
+      </c>
+      <c r="E153" t="s">
+        <v>873</v>
+      </c>
+      <c r="F153" t="s">
+        <v>874</v>
+      </c>
+      <c r="H153" s="2" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>876</v>
+      </c>
+      <c r="B154" t="s">
+        <v>686</v>
+      </c>
+      <c r="C154" t="s">
+        <v>877</v>
+      </c>
+      <c r="D154" t="s">
+        <v>242</v>
+      </c>
+      <c r="E154" t="s">
+        <v>878</v>
+      </c>
+      <c r="F154" t="s">
+        <v>688</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>880</v>
+      </c>
+      <c r="B155" t="s">
+        <v>316</v>
+      </c>
+      <c r="C155" t="s">
+        <v>881</v>
+      </c>
+      <c r="D155" t="s">
+        <v>242</v>
+      </c>
+      <c r="E155" t="s">
+        <v>579</v>
+      </c>
+      <c r="F155" t="s">
+        <v>882</v>
+      </c>
+      <c r="H155" s="2" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>884</v>
+      </c>
+      <c r="B156" t="s">
+        <v>885</v>
+      </c>
+      <c r="C156" t="s">
+        <v>342</v>
+      </c>
+      <c r="D156" t="s">
+        <v>242</v>
+      </c>
+      <c r="E156" t="s">
+        <v>886</v>
+      </c>
+      <c r="F156" t="s">
+        <v>887</v>
+      </c>
+      <c r="H156" s="2" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>889</v>
+      </c>
+      <c r="B157" t="s">
+        <v>890</v>
+      </c>
+      <c r="C157" t="s">
+        <v>891</v>
+      </c>
+      <c r="D157" t="s">
+        <v>422</v>
+      </c>
+      <c r="E157" t="s">
+        <v>892</v>
+      </c>
+      <c r="F157" t="s">
+        <v>893</v>
+      </c>
+      <c r="H157" s="2" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>889</v>
+      </c>
+      <c r="B158" t="s">
+        <v>895</v>
+      </c>
+      <c r="C158" t="s">
+        <v>248</v>
+      </c>
+      <c r="D158" t="s">
+        <v>242</v>
+      </c>
+      <c r="E158" t="s">
+        <v>896</v>
+      </c>
+      <c r="F158" t="s">
+        <v>897</v>
+      </c>
+      <c r="H158" s="2" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>899</v>
+      </c>
+      <c r="B159" t="s">
+        <v>900</v>
+      </c>
+      <c r="C159" t="s">
+        <v>901</v>
+      </c>
+      <c r="D159" t="s">
+        <v>242</v>
+      </c>
+      <c r="E159" t="s">
+        <v>902</v>
+      </c>
+      <c r="F159" t="s">
+        <v>903</v>
+      </c>
+      <c r="H159" s="2" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>905</v>
+      </c>
+      <c r="B160" t="s">
+        <v>906</v>
+      </c>
+      <c r="C160" t="s">
+        <v>368</v>
+      </c>
+      <c r="D160" t="s">
+        <v>242</v>
+      </c>
+      <c r="E160" t="s">
+        <v>907</v>
+      </c>
+      <c r="F160" t="s">
+        <v>908</v>
+      </c>
+      <c r="H160" s="2" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>910</v>
+      </c>
+      <c r="B161" t="s">
+        <v>890</v>
+      </c>
+      <c r="C161" t="s">
+        <v>891</v>
+      </c>
+      <c r="D161" t="s">
+        <v>422</v>
+      </c>
+      <c r="E161" t="s">
+        <v>892</v>
+      </c>
+      <c r="F161" t="s">
+        <v>893</v>
+      </c>
+      <c r="H161" s="2" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>912</v>
+      </c>
+      <c r="B162" t="s">
+        <v>890</v>
+      </c>
+      <c r="C162" t="s">
+        <v>891</v>
+      </c>
+      <c r="D162" t="s">
+        <v>422</v>
+      </c>
+      <c r="E162" t="s">
+        <v>892</v>
+      </c>
+      <c r="F162" t="s">
+        <v>893</v>
+      </c>
+      <c r="H162" s="2" t="s">
+        <v>913</v>
       </c>
     </row>
   </sheetData>
@@ -6187,6 +8126,65 @@
     <hyperlink ref="H101" r:id="rId100"/>
     <hyperlink ref="H102" r:id="rId101"/>
     <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
+    <hyperlink ref="H132" r:id="rId131"/>
+    <hyperlink ref="H133" r:id="rId132"/>
+    <hyperlink ref="H134" r:id="rId133"/>
+    <hyperlink ref="H135" r:id="rId134"/>
+    <hyperlink ref="H136" r:id="rId135"/>
+    <hyperlink ref="H137" r:id="rId136"/>
+    <hyperlink ref="H138" r:id="rId137"/>
+    <hyperlink ref="H139" r:id="rId138"/>
+    <hyperlink ref="H140" r:id="rId139"/>
+    <hyperlink ref="H141" r:id="rId140"/>
+    <hyperlink ref="H142" r:id="rId141"/>
+    <hyperlink ref="H143" r:id="rId142"/>
+    <hyperlink ref="H144" r:id="rId143"/>
+    <hyperlink ref="H145" r:id="rId144"/>
+    <hyperlink ref="H146" r:id="rId145"/>
+    <hyperlink ref="H147" r:id="rId146"/>
+    <hyperlink ref="H148" r:id="rId147"/>
+    <hyperlink ref="H149" r:id="rId148"/>
+    <hyperlink ref="H150" r:id="rId149"/>
+    <hyperlink ref="H151" r:id="rId150"/>
+    <hyperlink ref="H152" r:id="rId151"/>
+    <hyperlink ref="H153" r:id="rId152"/>
+    <hyperlink ref="H154" r:id="rId153"/>
+    <hyperlink ref="H155" r:id="rId154"/>
+    <hyperlink ref="H156" r:id="rId155"/>
+    <hyperlink ref="H157" r:id="rId156"/>
+    <hyperlink ref="H158" r:id="rId157"/>
+    <hyperlink ref="H159" r:id="rId158"/>
+    <hyperlink ref="H160" r:id="rId159"/>
+    <hyperlink ref="H161" r:id="rId160"/>
+    <hyperlink ref="H162" r:id="rId161"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
